--- a/poets_canonical.xlsx
+++ b/poets_canonical.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G296"/>
+  <dimension ref="A1:G297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,13 +475,11 @@
           <t>1448-1532</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -514,7 +512,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -547,7 +544,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -580,7 +576,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -613,7 +608,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -646,7 +640,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +672,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -712,7 +704,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -745,7 +736,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -778,7 +768,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -811,7 +800,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -881,7 +869,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -914,7 +901,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -947,7 +933,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -980,7 +965,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1013,7 +997,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1046,7 +1029,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1079,7 +1061,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1112,7 +1093,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1135,13 +1115,11 @@
           <t>1633 – 1718</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1174,7 +1152,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1207,7 +1184,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1240,7 +1216,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1273,7 +1248,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1306,7 +1280,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1339,7 +1312,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1372,7 +1344,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1405,7 +1376,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1438,7 +1408,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1471,7 +1440,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1504,7 +1472,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1537,7 +1504,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1570,7 +1536,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1593,7 +1558,6 @@
           <t>1650–1722</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>Edo</t>
@@ -1636,7 +1600,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1669,7 +1632,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1702,7 +1664,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1735,7 +1696,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1758,13 +1718,11 @@
           <t>1655—1733</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1797,7 +1755,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1830,7 +1787,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1853,13 +1809,11 @@
           <t>1656 – 1733</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1892,7 +1846,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1925,7 +1878,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1948,13 +1900,11 @@
           <t>1659 – 1717</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1987,7 +1937,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2010,13 +1959,11 @@
           <t>1661 – 1753</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2049,7 +1996,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2082,7 +2028,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2105,13 +2050,11 @@
           <t>1662 - 1726</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2144,7 +2087,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2177,7 +2119,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2210,7 +2151,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2233,13 +2173,11 @@
           <t>1663 – 1733</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2262,13 +2200,11 @@
           <t>1664–1726</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2301,7 +2237,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2334,7 +2269,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2357,13 +2291,11 @@
           <t>1669 – 1725</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2386,13 +2318,11 @@
           <t>1671－1742</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2415,13 +2345,11 @@
           <t>1672 – 1703</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2444,13 +2372,11 @@
           <t>1674 – 1761</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2473,13 +2399,11 @@
           <t>1675 – 1739</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2502,13 +2426,11 @@
           <t>1677 – 1742</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2531,13 +2453,11 @@
           <t>1681 – 1755</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2560,13 +2480,11 @@
           <t>1685 – 1751</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2589,13 +2507,11 @@
           <t>1688 – 1747</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2618,13 +2534,11 @@
           <t>1695-1779</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2647,13 +2561,11 @@
           <t>1695 – 1748</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2676,13 +2588,11 @@
           <t>1700 – 1750</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2705,13 +2615,11 @@
           <t>1701 – 1769</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2734,13 +2642,11 @@
           <t>1702 - 1783</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2763,13 +2669,11 @@
           <t>1703 – 1775</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2802,7 +2706,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2825,13 +2728,11 @@
           <t>1709 – 1771</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2854,13 +2755,11 @@
           <t>1713 – 1795</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2883,13 +2782,11 @@
           <t>1714 – 1781</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2922,7 +2819,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2945,13 +2841,11 @@
           <t>1716 – 1784</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2974,13 +2868,11 @@
           <t>1718 – 1783</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3003,13 +2895,11 @@
           <t>1718 – 1801</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3032,13 +2922,11 @@
           <t>1718 – 1787</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3071,7 +2959,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3094,13 +2981,11 @@
           <t>1719 – 1807</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3123,13 +3008,11 @@
           <t>1719 – 1774</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3162,7 +3045,6 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3185,13 +3067,11 @@
           <t>1722 - 1805</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3214,13 +3094,11 @@
           <t>1723 – 1803</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3243,13 +3121,11 @@
           <t>1726 – 1798</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3272,13 +3148,11 @@
           <t>1727-1771</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3301,13 +3175,11 @@
           <t>1729 – 1780</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3330,13 +3202,11 @@
           <t>1730 - 1778</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3359,13 +3229,11 @@
           <t>1731－1803</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3388,13 +3256,11 @@
           <t>1732-1795</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3417,13 +3283,11 @@
           <t>1732－1815</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3446,13 +3310,11 @@
           <t>1732 – 1792</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3475,13 +3337,11 @@
           <t>1734 – 1817</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3504,13 +3364,11 @@
           <t>1734 – 1809</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3533,13 +3391,11 @@
           <t>1738 – 1791</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3562,13 +3418,11 @@
           <t>1740 – 1791</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3591,13 +3445,11 @@
           <t>1741 – 1789</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3620,13 +3472,11 @@
           <t>1742 – 1812</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3649,13 +3499,11 @@
           <t>1745 – 1802</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3678,13 +3526,11 @@
           <t>1748 – 1814</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3707,13 +3553,11 @@
           <t>1749 – 1816</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3736,13 +3580,11 @@
           <t>1750－1813</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3765,13 +3607,11 @@
           <t>1752 – 1811</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3794,13 +3634,11 @@
           <t>1753-1826</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3842,458 +3680,432 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>emori-gekkyo</t>
+          <t>kumura-gyotai</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Emori Gekkyo</t>
+          <t>Kyōtai</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>江森月居</t>
+          <t>暁台</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1756 - 1824</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>1732–1792</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>5. Buson</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Founded Bōkō school; key figure in Tenmei-era haiku renaissance; close associate of Buson</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>iwama-otsuni</t>
+          <t>emori-gekkyo</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Iwama Otsuni</t>
+          <t>Emori Gekkyo</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>岩間乙二</t>
+          <t>江森月居</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>1756 – 1823</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr"/>
+          <t>1756 - 1824</t>
+        </is>
+      </c>
       <c r="F112" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>suzuki-michihiko</t>
+          <t>iwama-otsuni</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Suzuki Michihiko</t>
+          <t>Iwama Otsuni</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>鈴木道彦</t>
+          <t>岩間乙二</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>1757 – 1819</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
+          <t>1756 – 1823</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>fujimori-sobaku</t>
+          <t>suzuki-michihiko</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Fujimori Sobaku</t>
+          <t>Suzuki Michihiko</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>藤森素檗</t>
+          <t>鈴木道彦</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>1758-1821</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
+          <t>1757 – 1819</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ryokan</t>
+          <t>fujimori-sobaku</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ryōkan</t>
+          <t>Fujimori Sobaku</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>良寛</t>
+          <t>藤森素檗</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>1758-1831</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
+          <t>1758-1821</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>narita-sokyu</t>
+          <t>ryokan</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Narita Sōkyū</t>
+          <t>Ryōkan</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>成田蒼虬</t>
+          <t>良寛</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>1759-1842</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>1758-1831</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>sakai-hoitsu</t>
+          <t>narita-sokyu</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Sakai Hōitsu</t>
+          <t>Narita Sōkyū</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>酒井抱一</t>
+          <t>成田蒼虬</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>1761 – 1828</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>1759-1842</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>takebe-socho</t>
+          <t>sakai-hoitsu</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Takebe Sōchō</t>
+          <t>Sakai Hōitsu</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>建部巣兆</t>
+          <t>酒井抱一</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>1761 – 1814</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>1761 – 1828</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>tagawa-horo</t>
+          <t>takebe-socho</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tagawa Hōrō</t>
+          <t>Takebe Sōchō</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>田川鳳朗</t>
+          <t>建部巣兆</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1762 – 1845</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>1761 – 1814</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kobayashi-issa</t>
+          <t>tagawa-horo</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kobayashi Issa</t>
+          <t>Tagawa Hōrō</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>小林一茶</t>
+          <t>田川鳳朗</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1763 – 1827</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>1762 – 1845</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>tsuruda-takuchi</t>
+          <t>kobayashi-issa</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Tsuruda Takuchi</t>
+          <t>Kobayashi Issa</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>鶴田卓池</t>
+          <t>小林一茶</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>1768－1846</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>1763 – 1827</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>sakurai-baishitsu</t>
+          <t>tsuruda-takuchi</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sakurai Baishitsu</t>
+          <t>Tsuruda Takuchi</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>桜井梅室</t>
+          <t>鶴田卓池</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>1769-1852</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>1768－1846</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>shimizu-itsubyo</t>
+          <t>sakurai-baishitsu</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Shimizu Itsubyō</t>
+          <t>Sakurai Baishitsu</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>清水一瓢</t>
+          <t>桜井梅室</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>1770 – 1840</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
+          <t>1769-1852</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>torigoe-tosai</t>
+          <t>shimizu-itsubyo</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Torigoe Tōsai</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
+          <t>Shimizu Itsubyō</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>清水一瓢</t>
+        </is>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>1803 – 1890</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
+          <t>1770 – 1840</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>uchida-hyakken</t>
+          <t>torigoe-tosai</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Uchida Hyakken</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>内田百閒</t>
+          <t>Torigoe Tōsai</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>1889 — 1971</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
+          <t>1803 – 1890</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>katagiri-ryoho</t>
+          <t>uchida-hyakken</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Katagiri Ryōho</t>
+          <t>Uchida Hyakken</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>片桐良保</t>
+          <t>内田百閒</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>生没年不詳</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>2. Teimon</t>
+          <t>1889 — 1971</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4301,57 +4113,53 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kitamura-ryui</t>
+          <t>katagiri-ryoho</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Kitamura Ryūi</t>
+          <t>Katagiri Ryōho</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>喜多村立以</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
+          <t>片桐良保</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>生没年不詳</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2. Teimon</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>nakamura-fumikuni</t>
+          <t>kitamura-ryui</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Nakamura Fumikuni</t>
+          <t>Kitamura Ryūi</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>中村史邦</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>生没年不詳</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>4. Shōmon</t>
+          <t>喜多村立以</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4359,28 +4167,31 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>nichino</t>
+          <t>nakamura-fumikuni</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Nichinō</t>
+          <t>Nakamura Fumikuni</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>日能</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>中村史邦</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>生没年不詳</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2. Teimon</t>
+          <t>4. Shōmon</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4388,32 +4199,26 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>suganoya-takamasa</t>
+          <t>nichino</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Suganoya Takamasa</t>
+          <t>Nichinō</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>菅野谷高政</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>生没年不詳</t>
+          <t>日能</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3. Danrin</t>
+          <t>2. Teimon</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4421,22 +4226,21 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>tashiro-syoi</t>
+          <t>suganoya-takamasa</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Tashiro Syōi</t>
+          <t>Suganoya Takamasa</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>田代松意</t>
+          <t>菅野谷高政</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4454,144 +4258,129 @@
           <t>Edo</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>tenko</t>
+          <t>tashiro-syoi</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Tenko</t>
+          <t>Tashiro Syōi</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>天高</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
+          <t>田代松意</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>生没年不詳</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>3. Danrin</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr">
         <is>
           <t>Edo</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>inoue-seigetsu</t>
+          <t>tenko</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Inoue Seigetsu</t>
+          <t>Tenko</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>井上井月</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>1822-1887</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+          <t>天高</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Modern</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr"/>
+          <t>Edo</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>hozumi-eiki</t>
+          <t>inoue-seigetsu</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Hozumi Eiki</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
+          <t>Inoue Seigetsu</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>井上井月</t>
+        </is>
+      </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>1823-1904</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>1822-1887</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>masaoka-shiki</t>
+          <t>hozumi-eiki</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Masaoka Shiki</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>正岡子規</t>
+          <t>Hozumi Eiki</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>1864―1902</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
+          <t>1823-1904</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Founder of Nippon School</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>murakami-kijo</t>
+          <t>masaoka-shiki</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Murakami Kijō</t>
+          <t>Masaoka Shiki</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>村上鬼城</t>
+          <t>正岡子規</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>1865―1938</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Hototogisu</t>
+          <t>1864―1902</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -4601,29 +4390,29 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Taisho Hototogisu, Student of Kyoshi, deaf</t>
+          <t>Founder of Nippon School</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>nakamura-rakuten</t>
+          <t>murakami-kijo</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Nakamura Rakuten</t>
+          <t>Murakami Kijō</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>中村楽天</t>
+          <t>村上鬼城</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>1865 - 1939</t>
+          <t>1865―1938</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4638,123 +4427,122 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>ジャーナリスト 『国民之友』の編集者</t>
+          <t>Taisho Hototogisu, Student of Kyoshi, deaf</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>natsume-soseki</t>
+          <t>nakamura-rakuten</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Natsume Soseki</t>
+          <t>Nakamura Rakuten</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>夏目漱石</t>
+          <t>中村楽天</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>1867―1916</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
+          <t>1865 - 1939</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Hototogisu</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>ジャーナリスト 『国民之友』の編集者</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>matsuse-seisei</t>
+          <t>natsume-soseki</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Matsuse Seisei</t>
+          <t>Natsume Soseki</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>松瀬青々</t>
+          <t>夏目漱石</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>1869 - 1937</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
+          <t>1867―1916</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>shinohara-ontei</t>
+          <t>matsuse-seisei</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Shinohara Ontei</t>
+          <t>Matsuse Seisei</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>篠原温亭</t>
+          <t>松瀬青々</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>1872 - 1926</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
+          <t>1869 - 1937</t>
+        </is>
+      </c>
       <c r="F140" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>俳人、小説家 徳富蘇峰が主宰する「國民新聞」に勤め活躍した ホトトギス同人となり、正岡子規、高浜虚子らに俳句を学んだ 俳誌「土上（どじょう）」を嶋田青峰らと共に刊行した</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kawahigashi-hekigoto</t>
+          <t>shinohara-ontei</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Kawahigashi Hekigotō</t>
+          <t>Shinohara Ontei</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>河東碧梧桐</t>
+          <t>篠原温亭</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1873―1937</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr"/>
+          <t>1872 - 1926</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr">
         <is>
           <t>Modern</t>
@@ -4762,48 +4550,51 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>editor of the magazines Hototogisu自由律</t>
+          <t>俳人、小説家 徳富蘇峰が主宰する「國民新聞」に勤め活躍した ホトトギス同人となり、正岡子規、高浜虚子らに俳句を学んだ 俳誌「土上（どじょう）」を嶋田青峰らと共に刊行した</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kyoshi-takahama</t>
+          <t>kawahigashi-hekigoto</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Kyoshi Takahama</t>
+          <t>Kawahigashi Hekigotō</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>高浜虚子</t>
+          <t>河東碧梧桐</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>1874 – 1959</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
+          <t>1873―1937</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>editor of the magazines Hototogisu自由律</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>takahama-kyoshi</t>
+          <t>kyoshi-takahama</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Takahama Kyoshi</t>
+          <t>Kyoshi Takahama</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4813,105 +4604,95 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>1874―1959</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
+          <t>1874 – 1959</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Nihon school→Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>nishiyama-hakuun</t>
+          <t>takahama-kyoshi</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Nishiyama Hakuun</t>
+          <t>Takahama Kyoshi</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>西山泊雲</t>
+          <t>高浜虚子</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>1877-1944</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
+          <t>1874―1959</t>
+        </is>
+      </c>
       <c r="F144" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Nihon school→Hototogisu</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>nakatsuka-ippekiro</t>
+          <t>nishiyama-hakuun</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Nakatsuka Ippekirō</t>
+          <t>Nishiyama Hakuun</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>中塚一碧楼</t>
+          <t>西山泊雲</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>1879-1946</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
+          <t>1877-1944</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Free Rhythm, founder Sea Crimson</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>usuda-aro</t>
+          <t>nakatsuka-ippekiro</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Usuda Arō</t>
+          <t>Nakatsuka Ippekirō</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>臼田亞浪</t>
+          <t>中塚一碧楼</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>1879 - 1951</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
+          <t>1879-1946</t>
+        </is>
+      </c>
       <c r="F146" t="inlineStr">
         <is>
           <t>Modern</t>
@@ -4919,32 +4700,31 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>俳誌「石楠(しゃくなげ)」を創刊。新傾向と保守との中間派</t>
+          <t>Free Rhythm, founder Sea Crimson</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kubota-kuhonta</t>
+          <t>usuda-aro</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Kubota Kuhonta</t>
+          <t>Usuda Arō</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>久保田九品太</t>
+          <t>臼田亞浪</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>1881 - 19２６</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
+          <t>1879 - 1951</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr">
         <is>
           <t>Modern</t>
@@ -4952,34 +4732,29 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>俳句を正岡子規に師事し、のち高浜虚子に入門</t>
+          <t>俳誌「石楠(しゃくなげ)」を創刊。新傾向と保守との中間派</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>suzuki-hanamino</t>
+          <t>kubota-kuhonta</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Suzuki Hanamino</t>
+          <t>Kubota Kuhonta</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>鈴木花蓑</t>
+          <t>久保田九品太</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>1881 - 1942</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Hototogisu</t>
+          <t>1881 - 19２６</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -4987,63 +4762,65 @@
           <t>Modern</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>俳句を正岡子規に師事し、のち高浜虚子に入門</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>taneda-santoka</t>
+          <t>suzuki-hanamino</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Taneda Santōka</t>
+          <t>Suzuki Hanamino</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>種田山頭火</t>
+          <t>鈴木花蓑</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>1882 - 1940</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
+          <t>1881 - 1942</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Hototogisu</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Free Rhythm, Student of Seisensui, Free Rhythm, Student of Seisensui,</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>watanabe-suiha</t>
+          <t>taneda-santoka</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Watanabe Suiha</t>
+          <t>Taneda Santōka</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>渡辺水巴</t>
+          <t>種田山頭火</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>1882―1946</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
+          <t>1882 - 1940</t>
+        </is>
+      </c>
       <c r="F150" t="inlineStr">
         <is>
           <t>Modern</t>
@@ -5051,32 +4828,31 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Taisho Hototogisu</t>
+          <t>Free Rhythm, Student of Seisensui, Free Rhythm, Student of Seisensui,</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>maeda-fura</t>
+          <t>watanabe-suiha</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Maeda Fura</t>
+          <t>Watanabe Suiha</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>前田普羅</t>
+          <t>渡辺水巴</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>1884―1954</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr"/>
+          <t>1882―1946</t>
+        </is>
+      </c>
       <c r="F151" t="inlineStr">
         <is>
           <t>Modern</t>
@@ -5091,25 +4867,24 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ogiwara-seisensui</t>
+          <t>maeda-fura</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ogiwara Seisensui</t>
+          <t>Maeda Fura</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>荻原井泉水</t>
+          <t>前田普羅</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>1884―1976</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
+          <t>1884―1954</t>
+        </is>
+      </c>
       <c r="F152" t="inlineStr">
         <is>
           <t>Modern</t>
@@ -5117,94 +4892,90 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Nihon school→New Tendancy→Free Rhythm, Founder Sōun, Student of Hekigōtō, Teacher of Hōsai &amp; SantōkaNihon school→New Tendancy→Free Rhythm, Founder Sōun, Student of Hekigōtō, Teacher of Hōsai &amp; Santōka</t>
+          <t>Taisho Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>iida-dakotsu</t>
+          <t>ogiwara-seisensui</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Iida Dakotsu</t>
+          <t>Ogiwara Seisensui</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>飯田蛇笏</t>
+          <t>荻原井泉水</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>1885 – 1962</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
+          <t>1884―1976</t>
+        </is>
+      </c>
       <c r="F153" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Nihon school→New Tendancy→Free Rhythm, Founder Sōun, Student of Hekigōtō, Teacher of Hōsai &amp; SantōkaNihon school→New Tendancy→Free Rhythm, Founder Sōun, Student of Hekigōtō, Teacher of Hōsai &amp; Santōka</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ozaki-hosai</t>
+          <t>iida-dakotsu</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ozaki Hōsai</t>
+          <t>Iida Dakotsu</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>尾崎放哉</t>
+          <t>飯田蛇笏</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>1885-1926</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
+          <t>1885 – 1962</t>
+        </is>
+      </c>
       <c r="F154" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Free Rhythm, Student of Seisensui, Free Rhythm, Student of Seisensui,</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>tomiyasu-fusei</t>
+          <t>ozaki-hosai</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Tomiyasu Fūsei</t>
+          <t>Ozaki Hōsai</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>富安風生</t>
+          <t>尾崎放哉</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>1885 - 1979</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr"/>
+          <t>1885-1926</t>
+        </is>
+      </c>
       <c r="F155" t="inlineStr">
         <is>
           <t>Modern</t>
@@ -5212,32 +4983,31 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Ashibi, student of Kyoshi</t>
+          <t>Free Rhythm, Student of Seisensui, Free Rhythm, Student of Seisensui,</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>hara-sekitei</t>
+          <t>tomiyasu-fusei</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Hara Sekitei</t>
+          <t>Tomiyasu Fūsei</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>原石鼎</t>
+          <t>富安風生</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>1886―1951</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr"/>
+          <t>1885 - 1979</t>
+        </is>
+      </c>
       <c r="F156" t="inlineStr">
         <is>
           <t>Modern</t>
@@ -5245,243 +5015,230 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Taisho Hototogisu</t>
+          <t>Ashibi, student of Kyoshi</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>nomura-kishu</t>
+          <t>hara-sekitei</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Nomura Kishu</t>
+          <t>Hara Sekitei</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>野村喜舟</t>
+          <t>原石鼎</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1886-1983</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr"/>
+          <t>1886―1951</t>
+        </is>
+      </c>
       <c r="F157" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Taisho Hototogisu</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>hasegawa-kanajo</t>
+          <t>nomura-kishu</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Hasegawa Kanajo</t>
+          <t>Nomura Kishu</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>長谷川かな女</t>
+          <t>野村喜舟</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>1887 - 1969</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr"/>
+          <t>1886-1983</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kosugi-yoshi</t>
+          <t>hasegawa-kanajo</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Kosugi Yoshi</t>
+          <t>Hasegawa Kanajo</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>小杉余子</t>
+          <t>長谷川かな女</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>1888－1961</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr"/>
+          <t>1887 - 1969</t>
+        </is>
+      </c>
       <c r="F159" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>mantaro-kubota</t>
+          <t>kosugi-yoshi</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Mantarō Kubota</t>
+          <t>Kosugi Yoshi</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>久保田万太郎</t>
+          <t>小杉余子</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>1889 – 1963</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
+          <t>1888－1961</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>murau-saisei</t>
+          <t>mantaro-kubota</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Murau Saisei</t>
+          <t>Mantarō Kubota</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>室生犀星</t>
+          <t>久保田万太郎</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>1889―1962</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
+          <t>1889 – 1963</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Novelst</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>sugita-hisajo</t>
+          <t>murau-saisei</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Sugita Hisajo</t>
+          <t>Murau Saisei</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>杉田久女</t>
+          <t>室生犀星</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1890 - 1946</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr"/>
+          <t>1889―1962</t>
+        </is>
+      </c>
       <c r="F162" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Novelst</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>akutagawa-ryunosuke</t>
+          <t>sugita-hisajo</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Akutagawa Ryūnosuke</t>
+          <t>Sugita Hisajo</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>芥川龍之介</t>
+          <t>杉田久女</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>1892―1927</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
+          <t>1890 - 1946</t>
+        </is>
+      </c>
       <c r="F163" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Novelst</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>mizuhara-shuoshi</t>
+          <t>akutagawa-ryunosuke</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Mizuhara Shūōshi</t>
+          <t>Akutagawa Ryūnosuke</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>水原秋櫻子</t>
+          <t>芥川龍之介</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>1892-1981</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
+          <t>1892―1927</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr">
         <is>
           <t>Modern</t>
@@ -5489,317 +5246,304 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>4S Hototogisu</t>
+          <t>Novelst</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ryunosuke-akutagawa</t>
+          <t>mizuhara-shuoshi</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Ryūnosuke Akutagawa</t>
+          <t>Mizuhara Shūōshi</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>芥川龍之介</t>
+          <t>水原秋櫻子</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>1892 – 1927</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
+          <t>1892-1981</t>
+        </is>
+      </c>
       <c r="F165" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>4S Hototogisu</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>shibusawa-shutei</t>
+          <t>ryunosuke-akutagawa</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Shibusawa Shūtei</t>
+          <t>Ryūnosuke Akutagawa</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>渋沢渋亭</t>
+          <t>芥川龍之介</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>1892 - 1984</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr"/>
+          <t>1892 – 1927</t>
+        </is>
+      </c>
       <c r="F166" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Shibusawa Hideo　東宝会長,東映取締役を歴任。久保田万太郎主宰の「いとう句会」同人</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>yamaguchi-seison</t>
+          <t>shibusawa-shutei</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Yamaguchi Seison</t>
+          <t>Shibusawa Shūtei</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>山口青邨</t>
+          <t>渋沢渋亭</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>1892 – 1988</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr"/>
+          <t>1892 - 1984</t>
+        </is>
+      </c>
       <c r="F167" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Shibusawa Hideo　東宝会長,東映取締役を歴任。久保田万太郎主宰の「いとう句会」同人</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>yoshida-toyo</t>
+          <t>yamaguchi-seison</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Yoshida Tōyō</t>
+          <t>Yamaguchi Seison</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>吉田冬葉</t>
+          <t>山口青邨</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>1892－1956</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr"/>
+          <t>1892 – 1988</t>
+        </is>
+      </c>
       <c r="F168" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>takano-suju</t>
+          <t>yoshida-toyo</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Takano Sujū</t>
+          <t>Yoshida Tōyō</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>高野素十</t>
+          <t>吉田冬葉</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>1893-1976</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr"/>
+          <t>1892－1956</t>
+        </is>
+      </c>
       <c r="F169" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>4S Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kuribayashi-issekiro</t>
+          <t>takano-suju</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Kuribayashi Issekiro</t>
+          <t>Takano Sujū</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>栗林一石路</t>
+          <t>高野素十</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>1894-1961</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr"/>
+          <t>1893-1976</t>
+        </is>
+      </c>
       <c r="F170" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>4S Hototogisu</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>nishijima-bakunan</t>
+          <t>kuribayashi-issekiro</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Nishijima Bakunan</t>
+          <t>Kuribayashi Issekiro</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>西島麦南</t>
+          <t>栗林一石路</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>1895－1981</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr"/>
+          <t>1894-1961</t>
+        </is>
+      </c>
       <c r="F171" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ikazaki-kokyo</t>
+          <t>nishijima-bakunan</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ikazaki Kokyō</t>
+          <t>Nishijima Bakunan</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>五十崎古郷</t>
+          <t>西島麦南</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>1896－1935</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr"/>
+          <t>1895－1981</t>
+        </is>
+      </c>
       <c r="F172" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kawabata-bosha</t>
+          <t>ikazaki-kokyo</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Kawabata Bosha</t>
+          <t>Ikazaki Kokyō</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>川端茅舎</t>
+          <t>五十崎古郷</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1897-1941</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr"/>
+          <t>1896－1935</t>
+        </is>
+      </c>
       <c r="F173" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>tomita-mobbo</t>
+          <t>kawabata-bosha</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Tomita Mobbo</t>
+          <t>Kawabata Bosha</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>富田木歩</t>
+          <t>川端茅舎</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1897 - 1923</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr"/>
+          <t>1897-1941</t>
+        </is>
+      </c>
       <c r="F174" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>tomita-moppo</t>
+          <t>tomita-mobbo</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Tomita Moppo</t>
+          <t>Tomita Mobbo</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5809,424 +5553,392 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>1897 – 1923</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr"/>
+          <t>1897 - 1923</t>
+        </is>
+      </c>
       <c r="F175" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>awano-seiho</t>
+          <t>tomita-moppo</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Awano Seiho</t>
+          <t>Tomita Moppo</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>阿波野青畝</t>
+          <t>富田木歩</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1899-1992</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr"/>
+          <t>1897 – 1923</t>
+        </is>
+      </c>
       <c r="F176" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>4S Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>hashimoto-takako</t>
+          <t>awano-seiho</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Hashimoto Takako</t>
+          <t>Awano Seiho</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>橋本多佳子</t>
+          <t>阿波野青畝</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>1899‐1963</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
+          <t>1899-1992</t>
+        </is>
+      </c>
       <c r="F177" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>4S Hototogisu</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>oikawa-tei</t>
+          <t>hashimoto-takako</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Oikawa Tei</t>
+          <t>Hashimoto Takako</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>及川貞</t>
+          <t>橋本多佳子</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>1899 - 1993</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr"/>
+          <t>1899‐1963</t>
+        </is>
+      </c>
       <c r="F178" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kanao-umenokado</t>
+          <t>oikawa-tei</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Kanao Umenokado</t>
+          <t>Oikawa Tei</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>金尾梅の門</t>
+          <t>及川貞</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>1900 – 1980</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr"/>
+          <t>1899 - 1993</t>
+        </is>
+      </c>
       <c r="F179" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>nagata-koi</t>
+          <t>kanao-umenokado</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Nagata Kōi</t>
+          <t>Kanao Umenokado</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>永田耕衣</t>
+          <t>金尾梅の門</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>1900 - 1997</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr"/>
+          <t>1900 – 1980</t>
+        </is>
+      </c>
       <c r="F180" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>naito-toten</t>
+          <t>nagata-koi</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Naitō Toten</t>
+          <t>Nagata Kōi</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>内藤吐天</t>
+          <t>永田耕衣</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>1900- 1976</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr"/>
+          <t>1900 - 1997</t>
+        </is>
+      </c>
       <c r="F181" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>nakamura-teijo</t>
+          <t>naito-toten</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Nakamura Teijo</t>
+          <t>Naitō Toten</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>中村汀女;</t>
+          <t>内藤吐天</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1900 – 1988</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr"/>
+          <t>1900- 1976</t>
+        </is>
+      </c>
       <c r="F182" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>saito-sanki</t>
+          <t>nakamura-teijo</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Saitō Sanki</t>
+          <t>Nakamura Teijo</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>西東三鬼</t>
+          <t>中村汀女;</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>1900 - 1962</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr"/>
+          <t>1900 – 1988</t>
+        </is>
+      </c>
       <c r="F183" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>akimoto-fujio</t>
+          <t>saito-sanki</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Akimoto Fujio</t>
+          <t>Saitō Sanki</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>秋元不死男</t>
+          <t>西東三鬼</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1901 - 1977</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr"/>
+          <t>1900 - 1962</t>
+        </is>
+      </c>
       <c r="F184" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>hino-sojo</t>
+          <t>akimoto-fujio</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Hino Sōjō</t>
+          <t>Akimoto Fujio</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>日野草城</t>
+          <t>秋元不死男</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>1901 - 1956</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr"/>
+          <t>1901 - 1977</t>
+        </is>
+      </c>
       <c r="F185" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>nakamura-kusato</t>
+          <t>hino-sojo</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Nakamura Kusatō</t>
+          <t>Hino Sōjō</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>中村草田男</t>
+          <t>日野草城</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>1901‐1983</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr"/>
+          <t>1901 - 1956</t>
+        </is>
+      </c>
       <c r="F186" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>takahama-toshio</t>
+          <t>nakamura-kusato</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Takahama Toshio</t>
+          <t>Nakamura Kusatō</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>高濱年尾</t>
+          <t>中村草田男</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>1901-79</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr"/>
+          <t>1901‐1983</t>
+        </is>
+      </c>
       <c r="F187" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>yamaguchi-seishi</t>
+          <t>takahama-toshio</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Yamaguchi Seishi</t>
+          <t>Takahama Toshio</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>山口誓子</t>
+          <t>高濱年尾</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>1901 - 1994</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr"/>
+          <t>1901-79</t>
+        </is>
+      </c>
       <c r="F188" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>4S Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>minayoshi-souminayoshi-sou</t>
+          <t>yamaguchi-seishi</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Minayoshi SōuMinayoshi Sōu</t>
+          <t>Yamaguchi Seishi</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>皆吉爽雨</t>
+          <t>山口誓子</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>1902-1983</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr"/>
+          <t>1901 - 1994</t>
+        </is>
+      </c>
       <c r="F189" t="inlineStr">
         <is>
           <t>Modern</t>
@@ -6234,624 +5946,586 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>高浜虚子に師事し、『ホトトギス』に所属。俳人協会副会長を務めた。</t>
+          <t>4S Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>tomizawa-kakio</t>
+          <t>minayoshi-souminayoshi-sou</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Tomizawa Kakio</t>
+          <t>Minayoshi SōuMinayoshi Sōu</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>富澤赤黄男</t>
+          <t>皆吉爽雨</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>1902 - 1962</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr"/>
+          <t>1902-1983</t>
+        </is>
+      </c>
       <c r="F190" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>高浜虚子に師事し、『ホトトギス』に所属。俳人協会副会長を務めた。</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>hashimoto-mudo</t>
+          <t>tomizawa-kakio</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Hashimoto Mudō</t>
+          <t>Tomizawa Kakio</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>橋本夢道</t>
+          <t>富澤赤黄男</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>1903- 1974</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr"/>
+          <t>1902 - 1962</t>
+        </is>
+      </c>
       <c r="F191" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>hoshino-tatsuko</t>
+          <t>hashimoto-mudo</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Hoshino Tatsuko</t>
+          <t>Hashimoto Mudō</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>星野立子</t>
+          <t>橋本夢道</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>1903－1984</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr"/>
+          <t>1903- 1974</t>
+        </is>
+      </c>
       <c r="F192" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>shiba-fukio</t>
+          <t>hoshino-tatsuko</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Shiba Fukio</t>
+          <t>Hoshino Tatsuko</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>芝不器男</t>
+          <t>星野立子</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>1903－1930</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr"/>
+          <t>1903－1984</t>
+        </is>
+      </c>
       <c r="F193" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ono-rinka</t>
+          <t>shiba-fukio</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Ōno Rinka</t>
+          <t>Shiba Fukio</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>大野林火</t>
+          <t>芝不器男</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>1904-1982</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr"/>
+          <t>1903－1930</t>
+        </is>
+      </c>
       <c r="F194" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>俳人協会訪中団団長</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>hirahata-seito</t>
+          <t>ono-rinka</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Hirahata Seitō</t>
+          <t>Ōno Rinka</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>平畑静塔</t>
+          <t>大野林火</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>1905 - 1997</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr"/>
+          <t>1904-1982</t>
+        </is>
+      </c>
       <c r="F195" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>俳人協会訪中団団長</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>kato-shuson</t>
+          <t>hirahata-seito</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Katō Shūson</t>
+          <t>Hirahata Seitō</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>加藤楸邨</t>
+          <t>平畑静塔</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>1905 - 1993</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr"/>
+          <t>1905 - 1997</t>
+        </is>
+      </c>
       <c r="F196" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ishizuka-tomoji</t>
+          <t>kato-shuson</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Ishizuka Tomoji</t>
+          <t>Katō Shūson</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>石塚友二</t>
+          <t>加藤楸邨</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>1906 - 1986</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr"/>
+          <t>1905 - 1993</t>
+        </is>
+      </c>
       <c r="F197" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>matsumoto-takashi</t>
+          <t>ishizuka-tomoji</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Matsumoto Takashi</t>
+          <t>Ishizuka Tomoji</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>松本たかし</t>
+          <t>石塚友二</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>1906 - 1956</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr"/>
+          <t>1906 - 1986</t>
+        </is>
+      </c>
       <c r="F198" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>shinohara-hosaku</t>
+          <t>matsumoto-takashi</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Shinohara Hōsaku</t>
+          <t>Matsumoto Takashi</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>篠原鳳作</t>
+          <t>松本たかし</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>1906 - 1936</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr"/>
+          <t>1906 - 1956</t>
+        </is>
+      </c>
       <c r="F199" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>azumi-atsushi</t>
+          <t>shinohara-hosaku</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Azumi Atsushi</t>
+          <t>Shinohara Hōsaku</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>安住敦</t>
+          <t>篠原鳳作</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>1907-1988</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr"/>
+          <t>1906 - 1936</t>
+        </is>
+      </c>
       <c r="F200" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>新興俳句運動の日野草城が主宰する『旗艦』に参加するも、戦後、久保田万太郎を擁して大町糺とともに『春燈』を創刊。主宰となる。1982年～1987年、俳人協会会長。1984年～1986年、朝日俳壇選者</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>hasegawa-sosei</t>
+          <t>azumi-atsushi</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Hasegawa Sosei</t>
+          <t>Azumi Atsushi</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>長谷川素逝</t>
+          <t>安住敦</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>1907－1946</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr"/>
+          <t>1907-1988</t>
+        </is>
+      </c>
       <c r="F201" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>新興俳句運動の日野草城が主宰する『旗艦』に参加するも、戦後、久保田万太郎を擁して大町糺とともに『春燈』を創刊。主宰となる。1982年～1987年、俳人協会会長。1984年～1986年、朝日俳壇選者</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>hosomi-ayako</t>
+          <t>hasegawa-sosei</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Hosomi Ayako</t>
+          <t>Hasegawa Sosei</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>細見綾子</t>
+          <t>長谷川素逝</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>1907 - 1997</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr"/>
+          <t>1907－1946</t>
+        </is>
+      </c>
       <c r="F202" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>soma-senshi</t>
+          <t>hosomi-ayako</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Soma Senshi</t>
+          <t>Hosomi Ayako</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>相馬遷子</t>
+          <t>細見綾子</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>1908－1976</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr"/>
+          <t>1907 - 1997</t>
+        </is>
+      </c>
       <c r="F203" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ishibashi-tatsunosuke</t>
+          <t>soma-senshi</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Ishibashi Tatsunosuke</t>
+          <t>Soma Senshi</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>石橋辰之助</t>
+          <t>相馬遷子</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>1909 - 1948</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr"/>
+          <t>1908－1976</t>
+        </is>
+      </c>
       <c r="F204" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>kakurai-akio</t>
+          <t>ishibashi-tatsunosuke</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Kakurai Akio</t>
+          <t>Ishibashi Tatsunosuke</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>加倉井秋を</t>
+          <t>石橋辰之助</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>1909 - 1988</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr"/>
+          <t>1909 - 1948</t>
+        </is>
+      </c>
       <c r="F205" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>shinohara-bon</t>
+          <t>kakurai-akio</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Shinohara Bon</t>
+          <t>Kakurai Akio</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>篠原梵</t>
+          <t>加倉井秋を</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>1910 - 1975</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr"/>
+          <t>1909 - 1988</t>
+        </is>
+      </c>
       <c r="F206" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>takaya-sushu</t>
+          <t>shinohara-bon</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Takaya Sūshū</t>
+          <t>Shinohara Bon</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>高屋窓秋</t>
+          <t>篠原梵</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>1910－1999</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr"/>
+          <t>1910 - 1975</t>
+        </is>
+      </c>
       <c r="F207" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ishida-hakyo</t>
+          <t>takaya-sushu</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Ishida Hakyō</t>
+          <t>Takaya Sūshū</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>石田波郷</t>
+          <t>高屋窓秋</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>1913 - 1969</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr"/>
+          <t>1910－1999</t>
+        </is>
+      </c>
       <c r="F208" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>hayashi-sho</t>
+          <t>ishida-hakyo</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Hayashi Shō</t>
+          <t>Ishida Hakyō</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>林翔</t>
+          <t>石田波郷</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>1914 - 2009</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr"/>
+          <t>1913 - 1969</t>
+        </is>
+      </c>
       <c r="F209" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>林翔（はやし・しょう）は、能村登四郎と同じ國學院大學の同窓であり、卒業後に勤務した市川高等学校も一緒、俳句の歩みも水原秋櫻子の「馬酔木」から始まり、登四郎が「沖」を創刊してからは登四郎が亡くなるまで70年近く俳句の道を歩みつづけた同志である。</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>kinoshita-yuji</t>
+          <t>hayashi-sho</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Kinoshita Yūji</t>
+          <t>Hayashi Shō</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>木下夕爾</t>
+          <t>林翔</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>1914－1965</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr"/>
+          <t>1914 - 2009</t>
+        </is>
+      </c>
       <c r="F210" t="inlineStr">
         <is>
           <t>Modern</t>
@@ -6859,94 +6533,90 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>林翔の俳句の信条は、「俳句は、自分の心と対象物とがぶつかり合った瞬間に生まれる感動が、有季定型の短詩となったもの」であるという。もしかしたら常に考えていること、繰り返し見ていることの中で、ある時、ある瞬間にふっと17文字の俳句の形となるような気がしている。</t>
+          <t>林翔（はやし・しょう）は、能村登四郎と同じ國學院大學の同窓であり、卒業後に勤務した市川高等学校も一緒、俳句の歩みも水原秋櫻子の「馬酔木」から始まり、登四郎が「沖」を創刊してからは登四郎が亡くなるまで70年近く俳句の道を歩みつづけた同志である。</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>kadokawa-genyoshi</t>
+          <t>kinoshita-yuji</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Kadokawa Genyoshi</t>
+          <t>Kinoshita Yūji</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>角川源義</t>
+          <t>木下夕爾</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>1917－1975</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr"/>
+          <t>1914－1965</t>
+        </is>
+      </c>
       <c r="F211" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>林翔の俳句の信条は、「俳句は、自分の心と対象物とがぶつかり合った瞬間に生まれる感動が、有季定型の短詩となったもの」であるという。もしかしたら常に考えていること、繰り返し見ていることの中で、ある時、ある瞬間にふっと17文字の俳句の形となるような気がしている。</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kaneko-tota</t>
+          <t>kadokawa-genyoshi</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Kaneko Tōta</t>
+          <t>Kadokawa Genyoshi</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>金子兜太</t>
+          <t>角川源義</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>1919 - present</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr"/>
+          <t>1917－1975</t>
+        </is>
+      </c>
       <c r="F212" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>1983年より現代俳句協会会長、1987年より朝日俳壇選者</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>mori-sumio</t>
+          <t>kaneko-tota</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Mori Sumio</t>
+          <t>Kaneko Tōta</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>森澄雄</t>
+          <t>金子兜太</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>1919 - 2010</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr"/>
+          <t>1919 - present</t>
+        </is>
+      </c>
       <c r="F213" t="inlineStr">
         <is>
           <t>Modern</t>
@@ -6954,32 +6624,31 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Student of Shuson, part of Kanrai</t>
+          <t>1983年より現代俳句協会会長、1987年より朝日俳壇選者</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>iida-ryuta</t>
+          <t>mori-sumio</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Iida Ryūta</t>
+          <t>Mori Sumio</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>飯田龍太</t>
+          <t>森澄雄</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>1920 - 2007</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr"/>
+          <t>1919 - 2010</t>
+        </is>
+      </c>
       <c r="F214" t="inlineStr">
         <is>
           <t>Modern</t>
@@ -6987,32 +6656,31 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Son of Dakotsu,</t>
+          <t>Student of Shuson, part of Kanrai</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>kusumoto-kenkiti</t>
+          <t>iida-ryuta</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Kusumoto Kenkiti</t>
+          <t>Iida Ryūta</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>楠本憲吉</t>
+          <t>飯田龍太</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>1921-1988</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr"/>
+          <t>1920 - 2007</t>
+        </is>
+      </c>
       <c r="F215" t="inlineStr">
         <is>
           <t>Modern</t>
@@ -7020,210 +6688,198 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>日野草城に師事</t>
+          <t>Son of Dakotsu,</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>takayanagi-jushin</t>
+          <t>kusumoto-kenkiti</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Takayanagi Jūshin</t>
+          <t>Kusumoto Kenkiti</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>高柳重信</t>
+          <t>楠本憲吉</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>1923 - 1983</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr"/>
+          <t>1921-1988</t>
+        </is>
+      </c>
       <c r="F216" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>日野草城に師事</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>hayashi-kineo</t>
+          <t>takayanagi-jushin</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Hayashi Kineo</t>
+          <t>Takayanagi Jūshin</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>林田紀音夫</t>
+          <t>高柳重信</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>1924—1998</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr"/>
+          <t>1923 - 1983</t>
+        </is>
+      </c>
       <c r="F217" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>hoshino-bakukyujin</t>
+          <t>hayashi-kineo</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Hoshino Bakukyūjin</t>
+          <t>Hayashi Kineo</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>星野麥丘人</t>
+          <t>林田紀音夫</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>1925 - 2013</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr"/>
+          <t>1924—1998</t>
+        </is>
+      </c>
       <c r="F218" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>katsura-beicho</t>
+          <t>hoshino-bakukyujin</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Katsura Beichō</t>
+          <t>Hoshino Bakukyūjin</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>桂米朝</t>
+          <t>星野麥丘人</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>1925—2015</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr"/>
+          <t>1925 - 2013</t>
+        </is>
+      </c>
       <c r="F219" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>okai-shoji</t>
+          <t>katsura-beicho</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Okai Shōji</t>
+          <t>Katsura Beichō</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>岡井省二</t>
+          <t>桂米朝</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>1925 - 2001</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr"/>
+          <t>1925—2015</t>
+        </is>
+      </c>
       <c r="F220" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>takaba-shugyo</t>
+          <t>okai-shoji</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Takaba shugyō</t>
+          <t>Okai Shōji</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>鷹羽狩行</t>
+          <t>岡井省二</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>1930 - present</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr"/>
+          <t>1925 - 2001</t>
+        </is>
+      </c>
       <c r="F221" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>1948年「天狼」に入会し山口誓子に師事 俳人協会会長</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>inahata-teiko</t>
+          <t>takaba-shugyo</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Inahata Teiko</t>
+          <t>Takaba shugyō</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>稲畑汀子</t>
+          <t>鷹羽狩行</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>1931 - present</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr"/>
+          <t>1930 - present</t>
+        </is>
+      </c>
       <c r="F222" t="inlineStr">
         <is>
           <t>Modern</t>
@@ -7231,1891 +6887,1709 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>grandfather= Takahama Kyoshi. edits “Hototogisu” and selects for the Asahi Newspaper. president of the Japan Traditional Haiku Association, the director of the Kyoshi Memorial Museum and an adviser to Haiku International Association.</t>
+          <t>1948年「天狼」に入会し山口誓子に師事 俳人協会会長</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>jima-nagisao</t>
+          <t>inahata-teiko</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Jima Nagisao</t>
+          <t>Inahata Teiko</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>矢島渚男</t>
+          <t>稲畑汀子</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>1935—</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr"/>
+          <t>1931 - present</t>
+        </is>
+      </c>
       <c r="F223" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>grandfather= Takahama Kyoshi. edits “Hototogisu” and selects for the Asahi Newspaper. president of the Japan Traditional Haiku Association, the director of the Kyoshi Memorial Museum and an adviser to Haiku International Association.</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>momoko-kuroda</t>
+          <t>jima-nagisao</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Momoko Kuroda</t>
+          <t>Jima Nagisao</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>黒田杏子</t>
+          <t>矢島渚男</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>1938 -</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr"/>
+          <t>1935—</t>
+        </is>
+      </c>
       <c r="F224" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>kadokawa-haruki</t>
+          <t>momoko-kuroda</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Kadokawa Haruki</t>
+          <t>Momoko Kuroda</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>角川春樹</t>
+          <t>黒田杏子</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>1942 - present</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr"/>
+          <t>1938 -</t>
+        </is>
+      </c>
       <c r="F225" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>tsubouchi-nenten</t>
+          <t>kadokawa-haruki</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Tsubouchi Nenten</t>
+          <t>Kadokawa Haruki</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>坪内稔典</t>
+          <t>角川春樹</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1944- present</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr"/>
+          <t>1942 - present</t>
+        </is>
+      </c>
       <c r="F226" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>fujita-naoko</t>
+          <t>tsubouchi-nenten</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Fujita Naoko</t>
+          <t>Tsubouchi Nenten</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>藤田直子</t>
+          <t>坪内稔典</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>1950—</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr"/>
+          <t>1944- present</t>
+        </is>
+      </c>
       <c r="F227" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>natsuishi-banya</t>
+          <t>fujita-naoko</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Natsuishi Ban'ya</t>
+          <t>Fujita Naoko</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>夏石番矢</t>
+          <t>藤田直子</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>1955 - present</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr"/>
+          <t>1950—</t>
+        </is>
+      </c>
       <c r="F228" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>mochizuki-shu</t>
+          <t>natsuishi-banya</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Mochizuki Shū</t>
+          <t>Natsuishi Ban'ya</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>望月周</t>
+          <t>夏石番矢</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>1965—</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr"/>
+          <t>1955 - present</t>
+        </is>
+      </c>
       <c r="F229" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>goto-hinao</t>
+          <t>mochizuki-shu</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Gotō Hinao</t>
+          <t>Mochizuki Shū</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>後藤比奈夫</t>
+          <t>望月周</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>1971-</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr"/>
+          <t>1965—</t>
+        </is>
+      </c>
       <c r="F230" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>akagi-kakudo</t>
+          <t>goto-hinao</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Akagi Kakudo</t>
+          <t>Gotō Hinao</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>赤木格堂</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
+          <t>後藤比奈夫</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>1971-</t>
+        </is>
+      </c>
       <c r="F231" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ando-tochumenbo</t>
+          <t>akagi-kakudo</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Ando Tochumenbo</t>
+          <t>Akagi Kakudo</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>安藤橡面坊</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr"/>
+          <t>赤木格堂</t>
+        </is>
+      </c>
       <c r="F232" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>aoki-getto</t>
+          <t>ando-tochumenbo</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Aoki Getto</t>
+          <t>Ando Tochumenbo</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>青木月斗</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr"/>
+          <t>安藤橡面坊</t>
+        </is>
+      </c>
       <c r="F233" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>arima-rojin</t>
+          <t>aoki-getto</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Arima Rojin</t>
+          <t>Aoki Getto</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>有馬朗人</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
+          <t>青木月斗</t>
+        </is>
+      </c>
       <c r="F234" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>bainen</t>
+          <t>arima-rojin</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Bainen</t>
+          <t>Arima Rojin</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>梅年</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
+          <t>有馬朗人</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>baisha</t>
+          <t>bainen</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Baisha</t>
+          <t>Bainen</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>梅舎</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr"/>
+          <t>梅年</t>
+        </is>
+      </c>
       <c r="F236" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>busen</t>
+          <t>baisha</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Busen</t>
+          <t>Baisha</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>武仙</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr"/>
+          <t>梅舎</t>
+        </is>
+      </c>
       <c r="F237" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>enshi</t>
+          <t>busen</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Enshi</t>
+          <t>Busen</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>苑子</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
-      <c r="E238" t="inlineStr"/>
+          <t>武仙</t>
+        </is>
+      </c>
       <c r="F238" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>etsuji</t>
+          <t>enshi</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Etsuji</t>
+          <t>Enshi</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>乙二</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr"/>
+          <t>苑子</t>
+        </is>
+      </c>
       <c r="F239" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ezan</t>
+          <t>etsuji</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Ezan</t>
+          <t>Etsuji</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>等栽</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr"/>
+          <t>乙二</t>
+        </is>
+      </c>
       <c r="F240" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>fujii-tatsunosuke</t>
+          <t>ezan</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Fujii Tatsunosuke</t>
+          <t>Ezan</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>藤井秩之介</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr"/>
+          <t>等栽</t>
+        </is>
+      </c>
       <c r="F241" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>fukagawa-shoichiro</t>
+          <t>fujii-tatsunosuke</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Fukagawa Shoichiro</t>
+          <t>Fujii Tatsunosuke</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>深川正一郎</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr"/>
+          <t>藤井秩之介</t>
+        </is>
+      </c>
       <c r="F242" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>goto-kujiro</t>
+          <t>fukagawa-shoichiro</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Goto Kujiro</t>
+          <t>Fukagawa Shoichiro</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>五島雉子郎</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr"/>
+          <t>深川正一郎</t>
+        </is>
+      </c>
       <c r="F243" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>goto-yahan</t>
+          <t>goto-kujiro</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Goto Yahan</t>
+          <t>Goto Kujiro</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>後藤夜半</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr"/>
+          <t>五島雉子郎</t>
+        </is>
+      </c>
       <c r="F244" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>haku</t>
+          <t>goto-yahan</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Hakū</t>
+          <t>Goto Yahan</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>坡厄</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr"/>
-      <c r="E245" t="inlineStr"/>
+          <t>後藤夜半</t>
+        </is>
+      </c>
       <c r="F245" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>harumi</t>
+          <t>haku</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Harumi</t>
+          <t>Hakū</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>春湖</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
-      <c r="E246" t="inlineStr"/>
+          <t>坡厄</t>
+        </is>
+      </c>
       <c r="F246" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>hashimoto-keiji</t>
+          <t>harumi</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Hashimoto Keiji</t>
+          <t>Harumi</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>橋本鶏二</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr"/>
+          <t>春湖</t>
+        </is>
+      </c>
       <c r="F247" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>horiguchi-seimin</t>
+          <t>hashimoto-keiji</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Horiguchi Seimin</t>
+          <t>Hashimoto Keiji</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>堀口星眠</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr"/>
+          <t>橋本鶏二</t>
+        </is>
+      </c>
       <c r="F248" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>hoyu</t>
+          <t>horiguchi-seimin</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Hōyu</t>
+          <t>Horiguchi Seimin</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>方由</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr"/>
+          <t>堀口星眠</t>
+        </is>
+      </c>
       <c r="F249" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>isan</t>
+          <t>hoyu</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Isan</t>
+          <t>Hōyu</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>為山</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
+          <t>方由</t>
+        </is>
+      </c>
       <c r="F250" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ishibara-yatsuka</t>
+          <t>isan</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Ishibara Yatsuka</t>
+          <t>Isan</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>石原八束</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr"/>
+          <t>為山</t>
+        </is>
+      </c>
       <c r="F251" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>jugo</t>
+          <t>ishibara-yatsuka</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Jugo</t>
+          <t>Ishibara Yatsuka</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>重五</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+          <t>石原八束</t>
+        </is>
+      </c>
       <c r="F252" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>kakucho</t>
+          <t>jugo</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Kakucho</t>
+          <t>Jugo</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>覚澄</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr"/>
+          <t>重五</t>
+        </is>
+      </c>
       <c r="F253" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>kashiragi</t>
+          <t>kakucho</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Kashiragi</t>
+          <t>Kakucho</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>橿良</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr"/>
+          <t>覚澄</t>
+        </is>
+      </c>
       <c r="F254" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>kato-kakei</t>
+          <t>kashiragi</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Kato Kakei</t>
+          <t>Kashiragi</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>加藤かけい</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr"/>
+          <t>橿良</t>
+        </is>
+      </c>
       <c r="F255" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>kato-shuuson</t>
+          <t>kato-kakei</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Kato Shuuson</t>
+          <t>Kato Kakei</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>加藤秋邨</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr"/>
+          <t>加藤かけい</t>
+        </is>
+      </c>
       <c r="F256" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>kawashima-hokoshi</t>
+          <t>kato-shuuson</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Kawashima Hokoshi</t>
+          <t>Kato Shuuson</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>川島彷徨子</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr"/>
+          <t>加藤秋邨</t>
+        </is>
+      </c>
       <c r="F257" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>kiginsui</t>
+          <t>kawashima-hokoshi</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Kiginsui</t>
+          <t>Kawashima Hokoshi</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>言水</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr"/>
+          <t>川島彷徨子</t>
+        </is>
+      </c>
       <c r="F258" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>kiyohara-kaido</t>
+          <t>kiginsui</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Kiyohara Kaido</t>
+          <t>Kiginsui</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>清原枚童</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr"/>
-      <c r="E259" t="inlineStr"/>
+          <t>言水</t>
+        </is>
+      </c>
       <c r="F259" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>kiyosaki-toshio</t>
+          <t>kiyohara-kaido</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Kiyosaki Toshio</t>
+          <t>Kiyohara Kaido</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>清崎敏郎</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr"/>
+          <t>清原枚童</t>
+        </is>
+      </c>
       <c r="F260" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>kojima-shosho</t>
+          <t>kiyosaki-toshio</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Kojima Shosho</t>
+          <t>Kiyosaki Toshio</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>小島昌勝</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr"/>
+          <t>清崎敏郎</t>
+        </is>
+      </c>
       <c r="F261" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>kondo-ikko</t>
+          <t>kojima-shosho</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Kondo Ikko</t>
+          <t>Kojima Shosho</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>近藤一鴻</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
-      <c r="E262" t="inlineStr"/>
+          <t>小島昌勝</t>
+        </is>
+      </c>
       <c r="F262" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>kubo-yorie</t>
+          <t>kondo-ikko</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Kubo Yorie</t>
+          <t>Kondo Ikko</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>久保より江</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr"/>
+          <t>近藤一鴻</t>
+        </is>
+      </c>
       <c r="F263" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>masuda-ryuu</t>
+          <t>kubo-yorie</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Masuda Ryuu</t>
+          <t>Kubo Yorie</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>増田龍雨</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr"/>
+          <t>久保より江</t>
+        </is>
+      </c>
       <c r="F264" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>matsune-toyojo</t>
+          <t>masuda-ryuu</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Matsune Toyojo</t>
+          <t>Masuda Ryuu</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>松根東洋城</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr"/>
-      <c r="E265" t="inlineStr"/>
+          <t>増田龍雨</t>
+        </is>
+      </c>
       <c r="F265" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>matsuo-iwaho</t>
+          <t>matsune-toyojo</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Matsuo Iwaho</t>
+          <t>Matsune Toyojo</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>松尾いわほ</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr"/>
+          <t>松根東洋城</t>
+        </is>
+      </c>
       <c r="F266" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>miwa-seishu</t>
+          <t>matsuo-iwaho</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Miwa Seishu</t>
+          <t>Matsuo Iwaho</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>三輪清舟</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr"/>
+          <t>松尾いわほ</t>
+        </is>
+      </c>
       <c r="F267" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>mizutani-saiko</t>
+          <t>miwa-seishu</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Mizutani Saiko</t>
+          <t>Miwa Seishu</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>水谷碧霞</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
-      <c r="E268" t="inlineStr"/>
+          <t>三輪清舟</t>
+        </is>
+      </c>
       <c r="F268" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>nakamura-gessan</t>
+          <t>mizutani-saiko</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Nakamura Gessan</t>
+          <t>Mizutani Saiko</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>中村月三</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr"/>
+          <t>水谷碧霞</t>
+        </is>
+      </c>
       <c r="F269" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>niryu</t>
+          <t>nakamura-gessan</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Niryū</t>
+          <t>Nakamura Gessan</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>二柳</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr"/>
+          <t>中村月三</t>
+        </is>
+      </c>
       <c r="F270" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>nishi-fusanro</t>
+          <t>niryu</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Nishi Fusanro</t>
+          <t>Niryū</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>岸風三楼</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr"/>
-      <c r="E271" t="inlineStr"/>
+          <t>二柳</t>
+        </is>
+      </c>
       <c r="F271" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>nobume</t>
+          <t>nishi-fusanro</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Nobume</t>
+          <t>Nishi Fusanro</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>野梅</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr"/>
-      <c r="E272" t="inlineStr"/>
+          <t>岸風三楼</t>
+        </is>
+      </c>
       <c r="F272" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ohashi-etsuoshi</t>
+          <t>nobume</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Ohashi Etsuoshi</t>
+          <t>Nobume</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>大橋越央子</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr"/>
+          <t>野梅</t>
+        </is>
+      </c>
       <c r="F273" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>okamoto-shohin</t>
+          <t>ohashi-etsuoshi</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Okamoto Shohin</t>
+          <t>Ohashi Etsuoshi</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>岡本松浜</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
-      <c r="E274" t="inlineStr"/>
+          <t>大橋越央子</t>
+        </is>
+      </c>
       <c r="F274" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>omine-akira</t>
+          <t>okamoto-shohin</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Omine Akira</t>
+          <t>Okamoto Shohin</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>大峯あきら</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr"/>
+          <t>岡本松浜</t>
+        </is>
+      </c>
       <c r="F275" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>omori-domei</t>
+          <t>omine-akira</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Omori Domei</t>
+          <t>Omine Akira</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>大森桐明</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr"/>
+          <t>大峯あきら</t>
+        </is>
+      </c>
       <c r="F276" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>otokuni</t>
+          <t>omori-domei</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Otokuni</t>
+          <t>Omori Domei</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>乙由</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr"/>
+          <t>大森桐明</t>
+        </is>
+      </c>
       <c r="F277" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>saio</t>
+          <t>otokuni</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Saiō</t>
+          <t>Otokuni</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>西翁</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
-      <c r="E278" t="inlineStr"/>
+          <t>乙由</t>
+        </is>
+      </c>
       <c r="F278" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>sakaba-aijin</t>
+          <t>saio</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Sakaba Aijin</t>
+          <t>Saiō</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>酒葉露人</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
-      <c r="E279" t="inlineStr"/>
+          <t>西翁</t>
+        </is>
+      </c>
       <c r="F279" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>sano-ryota</t>
+          <t>sakaba-aijin</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Sano Ryota</t>
+          <t>Sakaba Aijin</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>佐野良太</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
-      <c r="E280" t="inlineStr"/>
+          <t>酒葉露人</t>
+        </is>
+      </c>
       <c r="F280" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>sawaki-kinichi</t>
+          <t>sano-ryota</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Sawaki Kinichi</t>
+          <t>Sano Ryota</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>澤木欣一</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
-      <c r="E281" t="inlineStr"/>
+          <t>佐野良太</t>
+        </is>
+      </c>
       <c r="F281" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>seifu</t>
+          <t>sawaki-kinichi</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Seifu</t>
+          <t>Sawaki Kinichi</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>星布</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
-      <c r="E282" t="inlineStr"/>
+          <t>澤木欣一</t>
+        </is>
+      </c>
       <c r="F282" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>shara</t>
+          <t>seifu</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Shara</t>
+          <t>Seifu</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>舎羅</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr"/>
-      <c r="E283" t="inlineStr"/>
+          <t>星布</t>
+        </is>
+      </c>
       <c r="F283" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>shimada-seiho</t>
+          <t>shara</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Shimada Seiho</t>
+          <t>Shara</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>島田青峰</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr"/>
-      <c r="E284" t="inlineStr"/>
+          <t>舎羅</t>
+        </is>
+      </c>
       <c r="F284" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>shoi</t>
+          <t>shimada-seiho</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Shōi</t>
+          <t>Shimada Seiho</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>松意</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
-      <c r="E285" t="inlineStr"/>
+          <t>島田青峰</t>
+        </is>
+      </c>
       <c r="F285" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>shosatsu</t>
+          <t>shoi</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Shōsatsu</t>
+          <t>Shōi</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>正察</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr"/>
-      <c r="E286" t="inlineStr"/>
+          <t>松意</t>
+        </is>
+      </c>
       <c r="F286" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>taimu</t>
+          <t>shosatsu</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Taimu</t>
+          <t>Shōsatsu</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>太無</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr"/>
-      <c r="E287" t="inlineStr"/>
+          <t>正察</t>
+        </is>
+      </c>
       <c r="F287" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>takada-choi</t>
+          <t>taimu</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Takada Choi</t>
+          <t>Taimu</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>高田蝶衣</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr"/>
-      <c r="E288" t="inlineStr"/>
+          <t>太無</t>
+        </is>
+      </c>
       <c r="F288" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>takahashi-awajijo</t>
+          <t>takada-choi</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Takahashi Awajijo</t>
+          <t>Takada Choi</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>高橋淡路女</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr"/>
-      <c r="E289" t="inlineStr"/>
+          <t>高田蝶衣</t>
+        </is>
+      </c>
       <c r="F289" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>tanaka-ojo</t>
+          <t>takahashi-awajijo</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Tanaka Ojo</t>
+          <t>Takahashi Awajijo</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>田中王城</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr"/>
+          <t>高橋淡路女</t>
+        </is>
+      </c>
       <c r="F290" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>tayo</t>
+          <t>tanaka-ojo</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Tayo</t>
+          <t>Tanaka Ojo</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>多代女</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr"/>
+          <t>田中王城</t>
+        </is>
+      </c>
       <c r="F291" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>tsuruyuki</t>
+          <t>tayo</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Tsuruyuki</t>
+          <t>Tayo</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>鶴永</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr"/>
+          <t>多代女</t>
+        </is>
+      </c>
       <c r="F292" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>uchida-bojo</t>
+          <t>tsuruyuki</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Uchida Bojo</t>
+          <t>Tsuruyuki</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>内田暮情</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr"/>
-      <c r="E293" t="inlineStr"/>
+          <t>鶴永</t>
+        </is>
+      </c>
       <c r="F293" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ueno-yasushi</t>
+          <t>uchida-bojo</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Ueno Yasushi</t>
+          <t>Uchida Bojo</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>上野泰</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr"/>
+          <t>内田暮情</t>
+        </is>
+      </c>
       <c r="F294" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>yoshioka-zenjido</t>
+          <t>ueno-yasushi</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Yoshioka Zenjido</t>
+          <t>Ueno Yasushi</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>吉岡禅寺洞</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr"/>
+          <t>上野泰</t>
+        </is>
+      </c>
       <c r="F295" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
+          <t>yoshioka-zenjido</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Yoshioka Zenjido</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>吉岡禅寺洞</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Modern</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
           <t>yuriyama-uko</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
+      <c r="B297" t="inlineStr">
         <is>
           <t>Yuriyama Uko</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr">
+      <c r="C297" t="inlineStr">
         <is>
           <t>百合山羽公</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr"/>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>Modern</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr"/>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Modern</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/poets_canonical.xlsx
+++ b/poets_canonical.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G297"/>
+  <dimension ref="A1:G296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3292,22 +3292,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kato-kyodai</t>
+          <t>takayanagi-sotan</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Katō Kyōdai</t>
+          <t>Takayanagi Sōtan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>加藤暁台</t>
+          <t>高柳荘丹</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1732 – 1792</t>
+          <t>1734 – 1817</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3319,22 +3319,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>takayanagi-sotan</t>
+          <t>ueda-mucho</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Takayanagi Sōtan</t>
+          <t>Ueda Muchō</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>高柳荘丹</t>
+          <t>上田無腸</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1734 – 1817</t>
+          <t>1734 – 1809</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3346,22 +3346,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ueda-mucho</t>
+          <t>kaya-shirao</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ueda Muchō</t>
+          <t>Kaya Shirao</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>上田無腸</t>
+          <t>加舎白雄</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>1734 – 1809</t>
+          <t>1738 – 1791</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3373,22 +3373,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kaya-shirao</t>
+          <t>matsuo-seira</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Kaya Shirao</t>
+          <t>Matsuo Seira</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>加舎白雄</t>
+          <t>松岡青蘿</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1738 – 1791</t>
+          <t>1740 – 1791</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3400,22 +3400,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>matsuo-seira</t>
+          <t>takai-kito</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Matsuo Seira</t>
+          <t>Takai Kitō</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>松岡青蘿</t>
+          <t>高井几菫</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1740 – 1791</t>
+          <t>1741 – 1789</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3427,22 +3427,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>takai-kito</t>
+          <t>inoue-shiro</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Takai Kitō</t>
+          <t>Inoue Shirō</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>高井几菫</t>
+          <t>井上土朗</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>1741 – 1789</t>
+          <t>1742 – 1812</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3454,22 +3454,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>inoue-shiro</t>
+          <t>kyu-shigyo</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Inoue Shirō</t>
+          <t>Kyū Shigyō</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>井上土朗</t>
+          <t>宮紫暁</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>1742 – 1812</t>
+          <t>1745 – 1802</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3481,22 +3481,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kyu-shigyo</t>
+          <t>kurita-chodo</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kyū Shigyō</t>
+          <t>Kurita Chodō</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>宮紫暁</t>
+          <t>栗田樗堂</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>1745 – 1802</t>
+          <t>1748 – 1814</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -3508,22 +3508,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kurita-chodo</t>
+          <t>natsume-seibi</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kurita Chodō</t>
+          <t>Natsume Seibi</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>栗田樗堂</t>
+          <t>夏目成美</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>1748 – 1814</t>
+          <t>1749 – 1816</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3535,22 +3535,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>natsume-seibi</t>
+          <t>tokoyoda-chosui</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Natsume Seibi</t>
+          <t>Tokoyoda Chōsui</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>夏目成美</t>
+          <t>常世田長翠</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1749 – 1816</t>
+          <t>1750－1813</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3562,22 +3562,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>tokoyoda-chosui</t>
+          <t>matsumura-getsukei</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Tokoyoda Chōsui</t>
+          <t>Matsumura Getsukei</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>常世田長翠</t>
+          <t>松村月渓</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1750－1813</t>
+          <t>1752 – 1811</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -3589,22 +3589,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>matsumura-getsukei</t>
+          <t>tagami-kikusha</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Matsumura Getsukei</t>
+          <t>Tagami Kikusha</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>松村月渓</t>
+          <t>田上菊舎</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1752 – 1811</t>
+          <t>1753-1826</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3616,49 +3616,59 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>tagami-kikusha</t>
+          <t>teiga</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tagami Kikusha</t>
+          <t>Teiga</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>田上菊舎</t>
+          <t>定雅</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>1753-1826</t>
+          <t>1755—1825</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>5. Buson</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>Edo</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Buson's pupil</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>teiga</t>
+          <t>kumura-gyotai</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Teiga</t>
+          <t>Kyōtai</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>定雅</t>
+          <t>暁台</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>1755—1825</t>
+          <t>1732–1792</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3673,66 +3683,56 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Buson's pupil</t>
+          <t>Founded Bōkō school; key figure in Tenmei-era haiku renaissance; close associate of Buson</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kumura-gyotai</t>
+          <t>emori-gekkyo</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kyōtai</t>
+          <t>Emori Gekkyo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>暁台</t>
+          <t>江森月居</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1732–1792</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>5. Buson</t>
+          <t>1756 - 1824</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
           <t>Edo</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Founded Bōkō school; key figure in Tenmei-era haiku renaissance; close associate of Buson</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>emori-gekkyo</t>
+          <t>iwama-otsuni</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Emori Gekkyo</t>
+          <t>Iwama Otsuni</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>江森月居</t>
+          <t>岩間乙二</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>1756 - 1824</t>
+          <t>1756 – 1823</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -3744,22 +3744,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>iwama-otsuni</t>
+          <t>suzuki-michihiko</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Iwama Otsuni</t>
+          <t>Suzuki Michihiko</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>岩間乙二</t>
+          <t>鈴木道彦</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>1756 – 1823</t>
+          <t>1757 – 1819</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -3771,22 +3771,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>suzuki-michihiko</t>
+          <t>fujimori-sobaku</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Suzuki Michihiko</t>
+          <t>Fujimori Sobaku</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>鈴木道彦</t>
+          <t>藤森素檗</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>1757 – 1819</t>
+          <t>1758-1821</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -3798,22 +3798,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>fujimori-sobaku</t>
+          <t>ryokan</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Fujimori Sobaku</t>
+          <t>Ryōkan</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>藤森素檗</t>
+          <t>良寛</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>1758-1821</t>
+          <t>1758-1831</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -3825,22 +3825,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ryokan</t>
+          <t>narita-sokyu</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ryōkan</t>
+          <t>Narita Sōkyū</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>良寛</t>
+          <t>成田蒼虬</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>1758-1831</t>
+          <t>1759-1842</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -3852,22 +3852,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>narita-sokyu</t>
+          <t>sakai-hoitsu</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Narita Sōkyū</t>
+          <t>Sakai Hōitsu</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>成田蒼虬</t>
+          <t>酒井抱一</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>1759-1842</t>
+          <t>1761 – 1828</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -3879,22 +3879,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>sakai-hoitsu</t>
+          <t>takebe-socho</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sakai Hōitsu</t>
+          <t>Takebe Sōchō</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>酒井抱一</t>
+          <t>建部巣兆</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>1761 – 1828</t>
+          <t>1761 – 1814</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -3906,22 +3906,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>takebe-socho</t>
+          <t>tagawa-horo</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Takebe Sōchō</t>
+          <t>Tagawa Hōrō</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>建部巣兆</t>
+          <t>田川鳳朗</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1761 – 1814</t>
+          <t>1762 – 1845</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -3933,22 +3933,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>tagawa-horo</t>
+          <t>kobayashi-issa</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Tagawa Hōrō</t>
+          <t>Kobayashi Issa</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>田川鳳朗</t>
+          <t>小林一茶</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1762 – 1845</t>
+          <t>1763 – 1827</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -3960,22 +3960,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kobayashi-issa</t>
+          <t>tsuruda-takuchi</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Kobayashi Issa</t>
+          <t>Tsuruda Takuchi</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>小林一茶</t>
+          <t>鶴田卓池</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>1763 – 1827</t>
+          <t>1768－1846</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -3987,22 +3987,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>tsuruda-takuchi</t>
+          <t>sakurai-baishitsu</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Tsuruda Takuchi</t>
+          <t>Sakurai Baishitsu</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>鶴田卓池</t>
+          <t>桜井梅室</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>1768－1846</t>
+          <t>1769-1852</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4014,22 +4014,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>sakurai-baishitsu</t>
+          <t>shimizu-itsubyo</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Sakurai Baishitsu</t>
+          <t>Shimizu Itsubyō</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>桜井梅室</t>
+          <t>清水一瓢</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>1769-1852</t>
+          <t>1770 – 1840</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4041,22 +4041,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>shimizu-itsubyo</t>
+          <t>torigoe-tosai</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Shimizu Itsubyō</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>清水一瓢</t>
+          <t>Torigoe Tōsai</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>1770 – 1840</t>
+          <t>1803 – 1890</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4068,17 +4063,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>torigoe-tosai</t>
+          <t>uchida-hyakken</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Torigoe Tōsai</t>
+          <t>Uchida Hyakken</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>内田百閒</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>1803 – 1890</t>
+          <t>1889 — 1971</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4090,22 +4090,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>uchida-hyakken</t>
+          <t>katagiri-ryoho</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Uchida Hyakken</t>
+          <t>Katagiri Ryōho</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>内田百閒</t>
+          <t>片桐良保</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>1889 — 1971</t>
+          <t>生没年不詳</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2. Teimon</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4117,27 +4122,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>katagiri-ryoho</t>
+          <t>kitamura-ryui</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Katagiri Ryōho</t>
+          <t>Kitamura Ryūi</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>片桐良保</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>生没年不詳</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>2. Teimon</t>
+          <t>喜多村立以</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4149,17 +4144,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kitamura-ryui</t>
+          <t>nakamura-fumikuni</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Kitamura Ryūi</t>
+          <t>Nakamura Fumikuni</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>喜多村立以</t>
+          <t>中村史邦</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>生没年不詳</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>4. Shōmon</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4171,27 +4176,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>nakamura-fumikuni</t>
+          <t>nichino</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Nakamura Fumikuni</t>
+          <t>Nichinō</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>中村史邦</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>生没年不詳</t>
+          <t>日能</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>4. Shōmon</t>
+          <t>2. Teimon</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4203,22 +4203,27 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>nichino</t>
+          <t>suganoya-takamasa</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nichinō</t>
+          <t>Suganoya Takamasa</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>日能</t>
+          <t>菅野谷高政</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>生没年不詳</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2. Teimon</t>
+          <t>3. Danrin</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4230,17 +4235,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>suganoya-takamasa</t>
+          <t>tashiro-syoi</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Suganoya Takamasa</t>
+          <t>Tashiro Syōi</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>菅野谷高政</t>
+          <t>田代松意</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4262,27 +4267,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>tashiro-syoi</t>
+          <t>tenko</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Tashiro Syōi</t>
+          <t>Tenko</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>田代松意</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>生没年不詳</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>3. Danrin</t>
+          <t>天高</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4294,44 +4289,44 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>tenko</t>
+          <t>inoue-seigetsu</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tenko</t>
+          <t>Inoue Seigetsu</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>天高</t>
+          <t>井上井月</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>1822-1887</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Edo</t>
+          <t>Modern</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>inoue-seigetsu</t>
+          <t>hozumi-eiki</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Inoue Seigetsu</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>井上井月</t>
+          <t>Hozumi Eiki</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>1822-1887</t>
+          <t>1823-1904</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -4343,44 +4338,59 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>hozumi-eiki</t>
+          <t>masaoka-shiki</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Hozumi Eiki</t>
+          <t>Masaoka Shiki</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>正岡子規</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>1823-1904</t>
+          <t>1864―1902</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
           <t>Modern</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Founder of Nippon School</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>masaoka-shiki</t>
+          <t>murakami-kijo</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Masaoka Shiki</t>
+          <t>Murakami Kijō</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>正岡子規</t>
+          <t>村上鬼城</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>1864―1902</t>
+          <t>1865―1938</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Hototogisu</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -4390,29 +4400,29 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Founder of Nippon School</t>
+          <t>Taisho Hototogisu, Student of Kyoshi, deaf</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>murakami-kijo</t>
+          <t>nakamura-rakuten</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Murakami Kijō</t>
+          <t>Nakamura Rakuten</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>村上鬼城</t>
+          <t>中村楽天</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>1865―1938</t>
+          <t>1865 - 1939</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4427,66 +4437,56 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Taisho Hototogisu, Student of Kyoshi, deaf</t>
+          <t>ジャーナリスト 『国民之友』の編集者</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>nakamura-rakuten</t>
+          <t>natsume-soseki</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Nakamura Rakuten</t>
+          <t>Natsume Soseki</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>中村楽天</t>
+          <t>夏目漱石</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>1865 - 1939</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Hototogisu</t>
+          <t>1867―1916</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>ジャーナリスト 『国民之友』の編集者</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>natsume-soseki</t>
+          <t>matsuse-seisei</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Natsume Soseki</t>
+          <t>Matsuse Seisei</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>夏目漱石</t>
+          <t>松瀬青々</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>1867―1916</t>
+          <t>1869 - 1937</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -4498,49 +4498,54 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>matsuse-seisei</t>
+          <t>shinohara-ontei</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Matsuse Seisei</t>
+          <t>Shinohara Ontei</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>松瀬青々</t>
+          <t>篠原温亭</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>1869 - 1937</t>
+          <t>1872 - 1926</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
           <t>Modern</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>俳人、小説家 徳富蘇峰が主宰する「國民新聞」に勤め活躍した ホトトギス同人となり、正岡子規、高浜虚子らに俳句を学んだ 俳誌「土上（どじょう）」を嶋田青峰らと共に刊行した</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>shinohara-ontei</t>
+          <t>kawahigashi-hekigoto</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Shinohara Ontei</t>
+          <t>Kawahigashi Hekigotō</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>篠原温亭</t>
+          <t>河東碧梧桐</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1872 - 1926</t>
+          <t>1873―1937</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -4550,51 +4555,46 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>俳人、小説家 徳富蘇峰が主宰する「國民新聞」に勤め活躍した ホトトギス同人となり、正岡子規、高浜虚子らに俳句を学んだ 俳誌「土上（どじょう）」を嶋田青峰らと共に刊行した</t>
+          <t>editor of the magazines Hototogisu自由律</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kawahigashi-hekigoto</t>
+          <t>kyoshi-takahama</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Kawahigashi Hekigotō</t>
+          <t>Kyoshi Takahama</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>河東碧梧桐</t>
+          <t>高浜虚子</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>1873―1937</t>
+          <t>1874 – 1959</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>editor of the magazines Hototogisu自由律</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kyoshi-takahama</t>
+          <t>takahama-kyoshi</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Kyoshi Takahama</t>
+          <t>Takahama Kyoshi</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4604,93 +4604,98 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>1874 – 1959</t>
+          <t>1874―1959</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
           <t>Modern</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Nihon school→Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>takahama-kyoshi</t>
+          <t>nishiyama-hakuun</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Takahama Kyoshi</t>
+          <t>Nishiyama Hakuun</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>高浜虚子</t>
+          <t>西山泊雲</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>1874―1959</t>
+          <t>1877-1944</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Nihon school→Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>nishiyama-hakuun</t>
+          <t>nakatsuka-ippekiro</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Nishiyama Hakuun</t>
+          <t>Nakatsuka Ippekirō</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>西山泊雲</t>
+          <t>中塚一碧楼</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>1877-1944</t>
+          <t>1879-1946</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
           <t>Modern</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Free Rhythm, founder Sea Crimson</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>nakatsuka-ippekiro</t>
+          <t>usuda-aro</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Nakatsuka Ippekirō</t>
+          <t>Usuda Arō</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>中塚一碧楼</t>
+          <t>臼田亞浪</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>1879-1946</t>
+          <t>1879 - 1951</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -4700,29 +4705,29 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Free Rhythm, founder Sea Crimson</t>
+          <t>俳誌「石楠(しゃくなげ)」を創刊。新傾向と保守との中間派</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>usuda-aro</t>
+          <t>kubota-kuhonta</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Usuda Arō</t>
+          <t>Kubota Kuhonta</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>臼田亞浪</t>
+          <t>久保田九品太</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>1879 - 1951</t>
+          <t>1881 - 19２６</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -4732,93 +4737,93 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>俳誌「石楠(しゃくなげ)」を創刊。新傾向と保守との中間派</t>
+          <t>俳句を正岡子規に師事し、のち高浜虚子に入門</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kubota-kuhonta</t>
+          <t>suzuki-hanamino</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Kubota Kuhonta</t>
+          <t>Suzuki Hanamino</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>久保田九品太</t>
+          <t>鈴木花蓑</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>1881 - 19２６</t>
+          <t>1881 - 1942</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Hototogisu</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>俳句を正岡子規に師事し、のち高浜虚子に入門</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>suzuki-hanamino</t>
+          <t>taneda-santoka</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Suzuki Hanamino</t>
+          <t>Taneda Santōka</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>鈴木花蓑</t>
+          <t>種田山頭火</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>1881 - 1942</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Hototogisu</t>
+          <t>1882 - 1940</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
           <t>Modern</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Free Rhythm, Student of Seisensui, Free Rhythm, Student of Seisensui,</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>taneda-santoka</t>
+          <t>watanabe-suiha</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Taneda Santōka</t>
+          <t>Watanabe Suiha</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>種田山頭火</t>
+          <t>渡辺水巴</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>1882 - 1940</t>
+          <t>1882―1946</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -4828,29 +4833,29 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Free Rhythm, Student of Seisensui, Free Rhythm, Student of Seisensui,</t>
+          <t>Taisho Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>watanabe-suiha</t>
+          <t>maeda-fura</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Watanabe Suiha</t>
+          <t>Maeda Fura</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>渡辺水巴</t>
+          <t>前田普羅</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>1882―1946</t>
+          <t>1884―1954</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -4867,22 +4872,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>maeda-fura</t>
+          <t>ogiwara-seisensui</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Maeda Fura</t>
+          <t>Ogiwara Seisensui</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>前田普羅</t>
+          <t>荻原井泉水</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>1884―1954</t>
+          <t>1884―1976</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -4892,88 +4897,88 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Taisho Hototogisu</t>
+          <t>Nihon school→New Tendancy→Free Rhythm, Founder Sōun, Student of Hekigōtō, Teacher of Hōsai &amp; SantōkaNihon school→New Tendancy→Free Rhythm, Founder Sōun, Student of Hekigōtō, Teacher of Hōsai &amp; Santōka</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ogiwara-seisensui</t>
+          <t>iida-dakotsu</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ogiwara Seisensui</t>
+          <t>Iida Dakotsu</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>荻原井泉水</t>
+          <t>飯田蛇笏</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>1884―1976</t>
+          <t>1885 – 1962</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Nihon school→New Tendancy→Free Rhythm, Founder Sōun, Student of Hekigōtō, Teacher of Hōsai &amp; SantōkaNihon school→New Tendancy→Free Rhythm, Founder Sōun, Student of Hekigōtō, Teacher of Hōsai &amp; Santōka</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>iida-dakotsu</t>
+          <t>ozaki-hosai</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Iida Dakotsu</t>
+          <t>Ozaki Hōsai</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>飯田蛇笏</t>
+          <t>尾崎放哉</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>1885 – 1962</t>
+          <t>1885-1926</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
           <t>Modern</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Free Rhythm, Student of Seisensui, Free Rhythm, Student of Seisensui,</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ozaki-hosai</t>
+          <t>tomiyasu-fusei</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ozaki Hōsai</t>
+          <t>Tomiyasu Fūsei</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>尾崎放哉</t>
+          <t>富安風生</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>1885-1926</t>
+          <t>1885 - 1979</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -4983,29 +4988,29 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Free Rhythm, Student of Seisensui, Free Rhythm, Student of Seisensui,</t>
+          <t>Ashibi, student of Kyoshi</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>tomiyasu-fusei</t>
+          <t>hara-sekitei</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Tomiyasu Fūsei</t>
+          <t>Hara Sekitei</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>富安風生</t>
+          <t>原石鼎</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>1885 - 1979</t>
+          <t>1886―1951</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5015,61 +5020,56 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ashibi, student of Kyoshi</t>
+          <t>Taisho Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>hara-sekitei</t>
+          <t>nomura-kishu</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Hara Sekitei</t>
+          <t>Nomura Kishu</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>原石鼎</t>
+          <t>野村喜舟</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1886―1951</t>
+          <t>1886-1983</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Taisho Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>nomura-kishu</t>
+          <t>hasegawa-kanajo</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Nomura Kishu</t>
+          <t>Hasegawa Kanajo</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>野村喜舟</t>
+          <t>長谷川かな女</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>1886-1983</t>
+          <t>1887 - 1969</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5081,22 +5081,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>hasegawa-kanajo</t>
+          <t>kosugi-yoshi</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Hasegawa Kanajo</t>
+          <t>Kosugi Yoshi</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>長谷川かな女</t>
+          <t>小杉余子</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>1887 - 1969</t>
+          <t>1888－1961</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5108,22 +5108,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kosugi-yoshi</t>
+          <t>mantaro-kubota</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Kosugi Yoshi</t>
+          <t>Mantarō Kubota</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>小杉余子</t>
+          <t>久保田万太郎</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>1888－1961</t>
+          <t>1889 – 1963</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -5135,108 +5135,113 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>mantaro-kubota</t>
+          <t>murau-saisei</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Mantarō Kubota</t>
+          <t>Murau Saisei</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>久保田万太郎</t>
+          <t>室生犀星</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>1889 – 1963</t>
+          <t>1889―1962</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
           <t>Modern</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Novelst</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>murau-saisei</t>
+          <t>sugita-hisajo</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Murau Saisei</t>
+          <t>Sugita Hisajo</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>室生犀星</t>
+          <t>杉田久女</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1889―1962</t>
+          <t>1890 - 1946</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Novelst</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>sugita-hisajo</t>
+          <t>akutagawa-ryunosuke</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Sugita Hisajo</t>
+          <t>Akutagawa Ryūnosuke</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>杉田久女</t>
+          <t>芥川龍之介</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>1890 - 1946</t>
+          <t>1892―1927</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
           <t>Modern</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Novelst</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>akutagawa-ryunosuke</t>
+          <t>mizuhara-shuoshi</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Akutagawa Ryūnosuke</t>
+          <t>Mizuhara Shūōshi</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>芥川龍之介</t>
+          <t>水原秋櫻子</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>1892―1927</t>
+          <t>1892-1981</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -5246,120 +5251,115 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Novelst</t>
+          <t>4S Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>mizuhara-shuoshi</t>
+          <t>ryunosuke-akutagawa</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Mizuhara Shūōshi</t>
+          <t>Ryūnosuke Akutagawa</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>水原秋櫻子</t>
+          <t>芥川龍之介</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>1892-1981</t>
+          <t>1892 – 1927</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>4S Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ryunosuke-akutagawa</t>
+          <t>shibusawa-shutei</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ryūnosuke Akutagawa</t>
+          <t>Shibusawa Shūtei</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>芥川龍之介</t>
+          <t>渋沢渋亭</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>1892 – 1927</t>
+          <t>1892 - 1984</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
           <t>Modern</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Shibusawa Hideo　東宝会長,東映取締役を歴任。久保田万太郎主宰の「いとう句会」同人</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>shibusawa-shutei</t>
+          <t>yamaguchi-seison</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Shibusawa Shūtei</t>
+          <t>Yamaguchi Seison</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>渋沢渋亭</t>
+          <t>山口青邨</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>1892 - 1984</t>
+          <t>1892 – 1988</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Shibusawa Hideo　東宝会長,東映取締役を歴任。久保田万太郎主宰の「いとう句会」同人</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>yamaguchi-seison</t>
+          <t>yoshida-toyo</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Yamaguchi Seison</t>
+          <t>Yoshida Tōyō</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>山口青邨</t>
+          <t>吉田冬葉</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>1892 – 1988</t>
+          <t>1892－1956</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -5371,81 +5371,81 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>yoshida-toyo</t>
+          <t>takano-suju</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Yoshida Tōyō</t>
+          <t>Takano Sujū</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>吉田冬葉</t>
+          <t>高野素十</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>1892－1956</t>
+          <t>1893-1976</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
           <t>Modern</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>4S Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>takano-suju</t>
+          <t>kuribayashi-issekiro</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Takano Sujū</t>
+          <t>Kuribayashi Issekiro</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>高野素十</t>
+          <t>栗林一石路</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>1893-1976</t>
+          <t>1894-1961</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>4S Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kuribayashi-issekiro</t>
+          <t>nishijima-bakunan</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Kuribayashi Issekiro</t>
+          <t>Nishijima Bakunan</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>栗林一石路</t>
+          <t>西島麦南</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>1894-1961</t>
+          <t>1895－1981</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -5457,22 +5457,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>nishijima-bakunan</t>
+          <t>ikazaki-kokyo</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Nishijima Bakunan</t>
+          <t>Ikazaki Kokyō</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>西島麦南</t>
+          <t>五十崎古郷</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>1895－1981</t>
+          <t>1896－1935</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -5484,22 +5484,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ikazaki-kokyo</t>
+          <t>kawabata-bosha</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ikazaki Kokyō</t>
+          <t>Kawabata Bosha</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>五十崎古郷</t>
+          <t>川端茅舎</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1896－1935</t>
+          <t>1897-1941</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -5511,22 +5511,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kawabata-bosha</t>
+          <t>tomita-mobbo</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Kawabata Bosha</t>
+          <t>Tomita Mobbo</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>川端茅舎</t>
+          <t>富田木歩</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1897-1941</t>
+          <t>1897 - 1923</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -5538,12 +5538,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>tomita-mobbo</t>
+          <t>tomita-moppo</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Tomita Mobbo</t>
+          <t>Tomita Moppo</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>1897 - 1923</t>
+          <t>1897 – 1923</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -5565,81 +5565,81 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>tomita-moppo</t>
+          <t>awano-seiho</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Tomita Moppo</t>
+          <t>Awano Seiho</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>富田木歩</t>
+          <t>阿波野青畝</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1897 – 1923</t>
+          <t>1899-1992</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
           <t>Modern</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>4S Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>awano-seiho</t>
+          <t>hashimoto-takako</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Awano Seiho</t>
+          <t>Hashimoto Takako</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>阿波野青畝</t>
+          <t>橋本多佳子</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>1899-1992</t>
+          <t>1899‐1963</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>4S Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>hashimoto-takako</t>
+          <t>oikawa-tei</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Hashimoto Takako</t>
+          <t>Oikawa Tei</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>橋本多佳子</t>
+          <t>及川貞</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>1899‐1963</t>
+          <t>1899 - 1993</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -5651,22 +5651,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>oikawa-tei</t>
+          <t>kanao-umenokado</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Oikawa Tei</t>
+          <t>Kanao Umenokado</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>及川貞</t>
+          <t>金尾梅の門</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>1899 - 1993</t>
+          <t>1900 – 1980</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -5678,22 +5678,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kanao-umenokado</t>
+          <t>nagata-koi</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Kanao Umenokado</t>
+          <t>Nagata Kōi</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>金尾梅の門</t>
+          <t>永田耕衣</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>1900 – 1980</t>
+          <t>1900 - 1997</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -5705,22 +5705,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>nagata-koi</t>
+          <t>naito-toten</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Nagata Kōi</t>
+          <t>Naitō Toten</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>永田耕衣</t>
+          <t>内藤吐天</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>1900 - 1997</t>
+          <t>1900- 1976</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -5732,22 +5732,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>naito-toten</t>
+          <t>nakamura-teijo</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Naitō Toten</t>
+          <t>Nakamura Teijo</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>内藤吐天</t>
+          <t>中村汀女;</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1900- 1976</t>
+          <t>1900 – 1988</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -5759,22 +5759,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>nakamura-teijo</t>
+          <t>saito-sanki</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Nakamura Teijo</t>
+          <t>Saitō Sanki</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>中村汀女;</t>
+          <t>西東三鬼</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>1900 – 1988</t>
+          <t>1900 - 1962</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -5786,22 +5786,22 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>saito-sanki</t>
+          <t>akimoto-fujio</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Saitō Sanki</t>
+          <t>Akimoto Fujio</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>西東三鬼</t>
+          <t>秋元不死男</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1900 - 1962</t>
+          <t>1901 - 1977</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -5813,22 +5813,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>akimoto-fujio</t>
+          <t>hino-sojo</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Akimoto Fujio</t>
+          <t>Hino Sōjō</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>秋元不死男</t>
+          <t>日野草城</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>1901 - 1977</t>
+          <t>1901 - 1956</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -5840,22 +5840,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>hino-sojo</t>
+          <t>nakamura-kusato</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Hino Sōjō</t>
+          <t>Nakamura Kusatō</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>日野草城</t>
+          <t>中村草田男</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>1901 - 1956</t>
+          <t>1901‐1983</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -5867,22 +5867,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>nakamura-kusato</t>
+          <t>takahama-toshio</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Nakamura Kusatō</t>
+          <t>Takahama Toshio</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>中村草田男</t>
+          <t>高濱年尾</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>1901‐1983</t>
+          <t>1901-79</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -5894,49 +5894,54 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>takahama-toshio</t>
+          <t>yamaguchi-seishi</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Takahama Toshio</t>
+          <t>Yamaguchi Seishi</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>高濱年尾</t>
+          <t>山口誓子</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>1901-79</t>
+          <t>1901 - 1994</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
           <t>Modern</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>4S Hototogisu</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>yamaguchi-seishi</t>
+          <t>minayoshi-souminayoshi-sou</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Yamaguchi Seishi</t>
+          <t>Minayoshi SōuMinayoshi Sōu</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>山口誓子</t>
+          <t>皆吉爽雨</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>1901 - 1994</t>
+          <t>1902-1983</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -5946,61 +5951,56 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>4S Hototogisu</t>
+          <t>高浜虚子に師事し、『ホトトギス』に所属。俳人協会副会長を務めた。</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>minayoshi-souminayoshi-sou</t>
+          <t>tomizawa-kakio</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Minayoshi SōuMinayoshi Sōu</t>
+          <t>Tomizawa Kakio</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>皆吉爽雨</t>
+          <t>富澤赤黄男</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>1902-1983</t>
+          <t>1902 - 1962</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>高浜虚子に師事し、『ホトトギス』に所属。俳人協会副会長を務めた。</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>tomizawa-kakio</t>
+          <t>hashimoto-mudo</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Tomizawa Kakio</t>
+          <t>Hashimoto Mudō</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>富澤赤黄男</t>
+          <t>橋本夢道</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>1902 - 1962</t>
+          <t>1903- 1974</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -6012,22 +6012,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>hashimoto-mudo</t>
+          <t>hoshino-tatsuko</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Hashimoto Mudō</t>
+          <t>Hoshino Tatsuko</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>橋本夢道</t>
+          <t>星野立子</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>1903- 1974</t>
+          <t>1903－1984</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -6039,22 +6039,22 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>hoshino-tatsuko</t>
+          <t>shiba-fukio</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Hoshino Tatsuko</t>
+          <t>Shiba Fukio</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>星野立子</t>
+          <t>芝不器男</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>1903－1984</t>
+          <t>1903－1930</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -6066,81 +6066,81 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>shiba-fukio</t>
+          <t>ono-rinka</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Shiba Fukio</t>
+          <t>Ōno Rinka</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>芝不器男</t>
+          <t>大野林火</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>1903－1930</t>
+          <t>1904-1982</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
           <t>Modern</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>俳人協会訪中団団長</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ono-rinka</t>
+          <t>hirahata-seito</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Ōno Rinka</t>
+          <t>Hirahata Seitō</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>大野林火</t>
+          <t>平畑静塔</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>1904-1982</t>
+          <t>1905 - 1997</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>俳人協会訪中団団長</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>hirahata-seito</t>
+          <t>kato-shuson</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Hirahata Seitō</t>
+          <t>Katō Shūson</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>平畑静塔</t>
+          <t>加藤楸邨</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>1905 - 1997</t>
+          <t>1905 - 1993</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -6152,22 +6152,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>kato-shuson</t>
+          <t>ishizuka-tomoji</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Katō Shūson</t>
+          <t>Ishizuka Tomoji</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>加藤楸邨</t>
+          <t>石塚友二</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>1905 - 1993</t>
+          <t>1906 - 1986</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -6179,22 +6179,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ishizuka-tomoji</t>
+          <t>matsumoto-takashi</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Ishizuka Tomoji</t>
+          <t>Matsumoto Takashi</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>石塚友二</t>
+          <t>松本たかし</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>1906 - 1986</t>
+          <t>1906 - 1956</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -6206,22 +6206,22 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>matsumoto-takashi</t>
+          <t>shinohara-hosaku</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Matsumoto Takashi</t>
+          <t>Shinohara Hōsaku</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>松本たかし</t>
+          <t>篠原鳳作</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>1906 - 1956</t>
+          <t>1906 - 1936</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -6233,81 +6233,81 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>shinohara-hosaku</t>
+          <t>azumi-atsushi</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Shinohara Hōsaku</t>
+          <t>Azumi Atsushi</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>篠原鳳作</t>
+          <t>安住敦</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>1906 - 1936</t>
+          <t>1907-1988</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
           <t>Modern</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>新興俳句運動の日野草城が主宰する『旗艦』に参加するも、戦後、久保田万太郎を擁して大町糺とともに『春燈』を創刊。主宰となる。1982年～1987年、俳人協会会長。1984年～1986年、朝日俳壇選者</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>azumi-atsushi</t>
+          <t>hasegawa-sosei</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Azumi Atsushi</t>
+          <t>Hasegawa Sosei</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>安住敦</t>
+          <t>長谷川素逝</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>1907-1988</t>
+          <t>1907－1946</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>新興俳句運動の日野草城が主宰する『旗艦』に参加するも、戦後、久保田万太郎を擁して大町糺とともに『春燈』を創刊。主宰となる。1982年～1987年、俳人協会会長。1984年～1986年、朝日俳壇選者</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>hasegawa-sosei</t>
+          <t>hosomi-ayako</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Hasegawa Sosei</t>
+          <t>Hosomi Ayako</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>長谷川素逝</t>
+          <t>細見綾子</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>1907－1946</t>
+          <t>1907 - 1997</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -6319,22 +6319,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>hosomi-ayako</t>
+          <t>soma-senshi</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Hosomi Ayako</t>
+          <t>Soma Senshi</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>細見綾子</t>
+          <t>相馬遷子</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>1907 - 1997</t>
+          <t>1908－1976</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -6346,22 +6346,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>soma-senshi</t>
+          <t>ishibashi-tatsunosuke</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Soma Senshi</t>
+          <t>Ishibashi Tatsunosuke</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>相馬遷子</t>
+          <t>石橋辰之助</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>1908－1976</t>
+          <t>1909 - 1948</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -6373,22 +6373,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ishibashi-tatsunosuke</t>
+          <t>kakurai-akio</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Ishibashi Tatsunosuke</t>
+          <t>Kakurai Akio</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>石橋辰之助</t>
+          <t>加倉井秋を</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>1909 - 1948</t>
+          <t>1909 - 1988</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -6400,22 +6400,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>kakurai-akio</t>
+          <t>shinohara-bon</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Kakurai Akio</t>
+          <t>Shinohara Bon</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>加倉井秋を</t>
+          <t>篠原梵</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>1909 - 1988</t>
+          <t>1910 - 1975</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -6427,22 +6427,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>shinohara-bon</t>
+          <t>takaya-sushu</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Shinohara Bon</t>
+          <t>Takaya Sūshū</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>篠原梵</t>
+          <t>高屋窓秋</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>1910 - 1975</t>
+          <t>1910－1999</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -6454,22 +6454,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>takaya-sushu</t>
+          <t>ishida-hakyo</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Takaya Sūshū</t>
+          <t>Ishida Hakyō</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>高屋窓秋</t>
+          <t>石田波郷</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>1910－1999</t>
+          <t>1913 - 1969</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -6481,49 +6481,54 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ishida-hakyo</t>
+          <t>hayashi-sho</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Ishida Hakyō</t>
+          <t>Hayashi Shō</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>石田波郷</t>
+          <t>林翔</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>1913 - 1969</t>
+          <t>1914 - 2009</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
           <t>Modern</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>林翔（はやし・しょう）は、能村登四郎と同じ國學院大學の同窓であり、卒業後に勤務した市川高等学校も一緒、俳句の歩みも水原秋櫻子の「馬酔木」から始まり、登四郎が「沖」を創刊してからは登四郎が亡くなるまで70年近く俳句の道を歩みつづけた同志である。</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>hayashi-sho</t>
+          <t>kinoshita-yuji</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Hayashi Shō</t>
+          <t>Kinoshita Yūji</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>林翔</t>
+          <t>木下夕爾</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>1914 - 2009</t>
+          <t>1914－1965</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -6533,88 +6538,88 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>林翔（はやし・しょう）は、能村登四郎と同じ國學院大學の同窓であり、卒業後に勤務した市川高等学校も一緒、俳句の歩みも水原秋櫻子の「馬酔木」から始まり、登四郎が「沖」を創刊してからは登四郎が亡くなるまで70年近く俳句の道を歩みつづけた同志である。</t>
+          <t>林翔の俳句の信条は、「俳句は、自分の心と対象物とがぶつかり合った瞬間に生まれる感動が、有季定型の短詩となったもの」であるという。もしかしたら常に考えていること、繰り返し見ていることの中で、ある時、ある瞬間にふっと17文字の俳句の形となるような気がしている。</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>kinoshita-yuji</t>
+          <t>kadokawa-genyoshi</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Kinoshita Yūji</t>
+          <t>Kadokawa Genyoshi</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>木下夕爾</t>
+          <t>角川源義</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>1914－1965</t>
+          <t>1917－1975</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>林翔の俳句の信条は、「俳句は、自分の心と対象物とがぶつかり合った瞬間に生まれる感動が、有季定型の短詩となったもの」であるという。もしかしたら常に考えていること、繰り返し見ていることの中で、ある時、ある瞬間にふっと17文字の俳句の形となるような気がしている。</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>kadokawa-genyoshi</t>
+          <t>kaneko-tota</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Kadokawa Genyoshi</t>
+          <t>Kaneko Tōta</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>角川源義</t>
+          <t>金子兜太</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>1917－1975</t>
+          <t>1919 - present</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
           <t>Modern</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>1983年より現代俳句協会会長、1987年より朝日俳壇選者</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>kaneko-tota</t>
+          <t>mori-sumio</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Kaneko Tōta</t>
+          <t>Mori Sumio</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>金子兜太</t>
+          <t>森澄雄</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>1919 - present</t>
+          <t>1919 - 2010</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -6624,29 +6629,29 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>1983年より現代俳句協会会長、1987年より朝日俳壇選者</t>
+          <t>Student of Shuson, part of Kanrai</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>mori-sumio</t>
+          <t>iida-ryuta</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Mori Sumio</t>
+          <t>Iida Ryūta</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>森澄雄</t>
+          <t>飯田龍太</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>1919 - 2010</t>
+          <t>1920 - 2007</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -6656,29 +6661,29 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Student of Shuson, part of Kanrai</t>
+          <t>Son of Dakotsu,</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>iida-ryuta</t>
+          <t>kusumoto-kenkiti</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Iida Ryūta</t>
+          <t>Kusumoto Kenkiti</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>飯田龍太</t>
+          <t>楠本憲吉</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>1920 - 2007</t>
+          <t>1921-1988</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -6688,61 +6693,56 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Son of Dakotsu,</t>
+          <t>日野草城に師事</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>kusumoto-kenkiti</t>
+          <t>takayanagi-jushin</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Kusumoto Kenkiti</t>
+          <t>Takayanagi Jūshin</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>楠本憲吉</t>
+          <t>高柳重信</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>1921-1988</t>
+          <t>1923 - 1983</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>日野草城に師事</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>takayanagi-jushin</t>
+          <t>hayashi-kineo</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Takayanagi Jūshin</t>
+          <t>Hayashi Kineo</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>高柳重信</t>
+          <t>林田紀音夫</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>1923 - 1983</t>
+          <t>1924—1998</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -6754,22 +6754,22 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>hayashi-kineo</t>
+          <t>hoshino-bakukyujin</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Hayashi Kineo</t>
+          <t>Hoshino Bakukyūjin</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>林田紀音夫</t>
+          <t>星野麥丘人</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>1924—1998</t>
+          <t>1925 - 2013</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -6781,22 +6781,22 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>hoshino-bakukyujin</t>
+          <t>katsura-beicho</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Hoshino Bakukyūjin</t>
+          <t>Katsura Beichō</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>星野麥丘人</t>
+          <t>桂米朝</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>1925 - 2013</t>
+          <t>1925—2015</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -6808,22 +6808,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>katsura-beicho</t>
+          <t>okai-shoji</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Katsura Beichō</t>
+          <t>Okai Shōji</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>桂米朝</t>
+          <t>岡井省二</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>1925—2015</t>
+          <t>1925 - 2001</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -6835,49 +6835,54 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>okai-shoji</t>
+          <t>takaba-shugyo</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Okai Shōji</t>
+          <t>Takaba shugyō</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>岡井省二</t>
+          <t>鷹羽狩行</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>1925 - 2001</t>
+          <t>1930 - present</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
           <t>Modern</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>1948年「天狼」に入会し山口誓子に師事 俳人協会会長</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>takaba-shugyo</t>
+          <t>inahata-teiko</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Takaba shugyō</t>
+          <t>Inahata Teiko</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>鷹羽狩行</t>
+          <t>稲畑汀子</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>1930 - present</t>
+          <t>1931 - present</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -6887,61 +6892,56 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>1948年「天狼」に入会し山口誓子に師事 俳人協会会長</t>
+          <t>grandfather= Takahama Kyoshi. edits “Hototogisu” and selects for the Asahi Newspaper. president of the Japan Traditional Haiku Association, the director of the Kyoshi Memorial Museum and an adviser to Haiku International Association.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>inahata-teiko</t>
+          <t>jima-nagisao</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Inahata Teiko</t>
+          <t>Jima Nagisao</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>稲畑汀子</t>
+          <t>矢島渚男</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>1931 - present</t>
+          <t>1935—</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
           <t>Modern</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>grandfather= Takahama Kyoshi. edits “Hototogisu” and selects for the Asahi Newspaper. president of the Japan Traditional Haiku Association, the director of the Kyoshi Memorial Museum and an adviser to Haiku International Association.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>jima-nagisao</t>
+          <t>momoko-kuroda</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Jima Nagisao</t>
+          <t>Momoko Kuroda</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>矢島渚男</t>
+          <t>黒田杏子</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>1935—</t>
+          <t>1938 -</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -6953,22 +6953,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>momoko-kuroda</t>
+          <t>kadokawa-haruki</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Momoko Kuroda</t>
+          <t>Kadokawa Haruki</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>黒田杏子</t>
+          <t>角川春樹</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>1938 -</t>
+          <t>1942 - present</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -6980,22 +6980,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>kadokawa-haruki</t>
+          <t>tsubouchi-nenten</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Kadokawa Haruki</t>
+          <t>Tsubouchi Nenten</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>角川春樹</t>
+          <t>坪内稔典</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1942 - present</t>
+          <t>1944- present</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -7007,22 +7007,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>tsubouchi-nenten</t>
+          <t>fujita-naoko</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Tsubouchi Nenten</t>
+          <t>Fujita Naoko</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>坪内稔典</t>
+          <t>藤田直子</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>1944- present</t>
+          <t>1950—</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -7034,22 +7034,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>fujita-naoko</t>
+          <t>natsuishi-banya</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Fujita Naoko</t>
+          <t>Natsuishi Ban'ya</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>藤田直子</t>
+          <t>夏石番矢</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>1950—</t>
+          <t>1955 - present</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -7061,22 +7061,22 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>natsuishi-banya</t>
+          <t>mochizuki-shu</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Natsuishi Ban'ya</t>
+          <t>Mochizuki Shū</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>夏石番矢</t>
+          <t>望月周</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>1955 - present</t>
+          <t>1965—</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -7088,22 +7088,22 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>mochizuki-shu</t>
+          <t>goto-hinao</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Mochizuki Shū</t>
+          <t>Gotō Hinao</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>望月周</t>
+          <t>後藤比奈夫</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>1965—</t>
+          <t>1971-</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -7115,22 +7115,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>goto-hinao</t>
+          <t>akagi-kakudo</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Gotō Hinao</t>
+          <t>Akagi Kakudo</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>後藤比奈夫</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>1971-</t>
+          <t>赤木格堂</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -7142,17 +7137,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>akagi-kakudo</t>
+          <t>ando-tochumenbo</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Akagi Kakudo</t>
+          <t>Ando Tochumenbo</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>赤木格堂</t>
+          <t>安藤橡面坊</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -7164,17 +7159,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ando-tochumenbo</t>
+          <t>aoki-getto</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Ando Tochumenbo</t>
+          <t>Aoki Getto</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>安藤橡面坊</t>
+          <t>青木月斗</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -7186,17 +7181,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>aoki-getto</t>
+          <t>arima-rojin</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Aoki Getto</t>
+          <t>Arima Rojin</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>青木月斗</t>
+          <t>有馬朗人</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -7208,17 +7203,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>arima-rojin</t>
+          <t>bainen</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Arima Rojin</t>
+          <t>Bainen</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>有馬朗人</t>
+          <t>梅年</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -7230,17 +7225,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>bainen</t>
+          <t>baisha</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Bainen</t>
+          <t>Baisha</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>梅年</t>
+          <t>梅舎</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -7252,17 +7247,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>baisha</t>
+          <t>busen</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Baisha</t>
+          <t>Busen</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>梅舎</t>
+          <t>武仙</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -7274,17 +7269,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>busen</t>
+          <t>enshi</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Busen</t>
+          <t>Enshi</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>武仙</t>
+          <t>苑子</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -7296,17 +7291,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>enshi</t>
+          <t>etsuji</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Enshi</t>
+          <t>Etsuji</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>苑子</t>
+          <t>乙二</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -7318,17 +7313,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>etsuji</t>
+          <t>ezan</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Etsuji</t>
+          <t>Ezan</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>乙二</t>
+          <t>等栽</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -7340,17 +7335,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ezan</t>
+          <t>fujii-tatsunosuke</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Ezan</t>
+          <t>Fujii Tatsunosuke</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>等栽</t>
+          <t>藤井秩之介</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -7362,17 +7357,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>fujii-tatsunosuke</t>
+          <t>fukagawa-shoichiro</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Fujii Tatsunosuke</t>
+          <t>Fukagawa Shoichiro</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>藤井秩之介</t>
+          <t>深川正一郎</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -7384,17 +7379,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>fukagawa-shoichiro</t>
+          <t>goto-kujiro</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Fukagawa Shoichiro</t>
+          <t>Goto Kujiro</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>深川正一郎</t>
+          <t>五島雉子郎</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -7406,17 +7401,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>goto-kujiro</t>
+          <t>goto-yahan</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Goto Kujiro</t>
+          <t>Goto Yahan</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>五島雉子郎</t>
+          <t>後藤夜半</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -7428,17 +7423,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>goto-yahan</t>
+          <t>haku</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Goto Yahan</t>
+          <t>Hakū</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>後藤夜半</t>
+          <t>坡厄</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -7450,17 +7445,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>haku</t>
+          <t>harumi</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Hakū</t>
+          <t>Harumi</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>坡厄</t>
+          <t>春湖</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -7472,17 +7467,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>harumi</t>
+          <t>hashimoto-keiji</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Harumi</t>
+          <t>Hashimoto Keiji</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>春湖</t>
+          <t>橋本鶏二</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -7494,17 +7489,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>hashimoto-keiji</t>
+          <t>horiguchi-seimin</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Hashimoto Keiji</t>
+          <t>Horiguchi Seimin</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>橋本鶏二</t>
+          <t>堀口星眠</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -7516,17 +7511,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>horiguchi-seimin</t>
+          <t>hoyu</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Horiguchi Seimin</t>
+          <t>Hōyu</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>堀口星眠</t>
+          <t>方由</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -7538,17 +7533,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>hoyu</t>
+          <t>isan</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Hōyu</t>
+          <t>Isan</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>方由</t>
+          <t>為山</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -7560,17 +7555,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>isan</t>
+          <t>ishibara-yatsuka</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Isan</t>
+          <t>Ishibara Yatsuka</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>為山</t>
+          <t>石原八束</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -7582,17 +7577,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ishibara-yatsuka</t>
+          <t>jugo</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Ishibara Yatsuka</t>
+          <t>Jugo</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>石原八束</t>
+          <t>重五</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -7604,17 +7599,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>jugo</t>
+          <t>kakucho</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Jugo</t>
+          <t>Kakucho</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>重五</t>
+          <t>覚澄</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -7626,17 +7621,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>kakucho</t>
+          <t>kashiragi</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Kakucho</t>
+          <t>Kashiragi</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>覚澄</t>
+          <t>橿良</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -7648,17 +7643,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>kashiragi</t>
+          <t>kato-kakei</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Kashiragi</t>
+          <t>Kato Kakei</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>橿良</t>
+          <t>加藤かけい</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -7670,17 +7665,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>kato-kakei</t>
+          <t>kato-shuuson</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Kato Kakei</t>
+          <t>Kato Shuuson</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>加藤かけい</t>
+          <t>加藤秋邨</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -7692,17 +7687,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>kato-shuuson</t>
+          <t>kawashima-hokoshi</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Kato Shuuson</t>
+          <t>Kawashima Hokoshi</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>加藤秋邨</t>
+          <t>川島彷徨子</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -7714,17 +7709,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>kawashima-hokoshi</t>
+          <t>kiginsui</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Kawashima Hokoshi</t>
+          <t>Kiginsui</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>川島彷徨子</t>
+          <t>言水</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -7736,17 +7731,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>kiginsui</t>
+          <t>kiyohara-kaido</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Kiginsui</t>
+          <t>Kiyohara Kaido</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>言水</t>
+          <t>清原枚童</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -7758,17 +7753,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>kiyohara-kaido</t>
+          <t>kiyosaki-toshio</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Kiyohara Kaido</t>
+          <t>Kiyosaki Toshio</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>清原枚童</t>
+          <t>清崎敏郎</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -7780,17 +7775,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>kiyosaki-toshio</t>
+          <t>kojima-shosho</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Kiyosaki Toshio</t>
+          <t>Kojima Shosho</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>清崎敏郎</t>
+          <t>小島昌勝</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -7802,17 +7797,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>kojima-shosho</t>
+          <t>kondo-ikko</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Kojima Shosho</t>
+          <t>Kondo Ikko</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>小島昌勝</t>
+          <t>近藤一鴻</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -7824,17 +7819,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>kondo-ikko</t>
+          <t>kubo-yorie</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Kondo Ikko</t>
+          <t>Kubo Yorie</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>近藤一鴻</t>
+          <t>久保より江</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -7846,17 +7841,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>kubo-yorie</t>
+          <t>masuda-ryuu</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Kubo Yorie</t>
+          <t>Masuda Ryuu</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>久保より江</t>
+          <t>増田龍雨</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -7868,17 +7863,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>masuda-ryuu</t>
+          <t>matsune-toyojo</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Masuda Ryuu</t>
+          <t>Matsune Toyojo</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>増田龍雨</t>
+          <t>松根東洋城</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -7890,17 +7885,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>matsune-toyojo</t>
+          <t>matsuo-iwaho</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Matsune Toyojo</t>
+          <t>Matsuo Iwaho</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>松根東洋城</t>
+          <t>松尾いわほ</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -7912,17 +7907,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>matsuo-iwaho</t>
+          <t>miwa-seishu</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Matsuo Iwaho</t>
+          <t>Miwa Seishu</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>松尾いわほ</t>
+          <t>三輪清舟</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -7934,17 +7929,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>miwa-seishu</t>
+          <t>mizutani-saiko</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Miwa Seishu</t>
+          <t>Mizutani Saiko</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>三輪清舟</t>
+          <t>水谷碧霞</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -7956,17 +7951,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>mizutani-saiko</t>
+          <t>nakamura-gessan</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Mizutani Saiko</t>
+          <t>Nakamura Gessan</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>水谷碧霞</t>
+          <t>中村月三</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -7978,17 +7973,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>nakamura-gessan</t>
+          <t>niryu</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Nakamura Gessan</t>
+          <t>Niryū</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>中村月三</t>
+          <t>二柳</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -8000,17 +7995,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>niryu</t>
+          <t>nishi-fusanro</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Niryū</t>
+          <t>Nishi Fusanro</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>二柳</t>
+          <t>岸風三楼</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -8022,17 +8017,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>nishi-fusanro</t>
+          <t>nobume</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Nishi Fusanro</t>
+          <t>Nobume</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>岸風三楼</t>
+          <t>野梅</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -8044,17 +8039,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>nobume</t>
+          <t>ohashi-etsuoshi</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Nobume</t>
+          <t>Ohashi Etsuoshi</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>野梅</t>
+          <t>大橋越央子</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -8066,17 +8061,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ohashi-etsuoshi</t>
+          <t>okamoto-shohin</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Ohashi Etsuoshi</t>
+          <t>Okamoto Shohin</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>大橋越央子</t>
+          <t>岡本松浜</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -8088,17 +8083,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>okamoto-shohin</t>
+          <t>omine-akira</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Okamoto Shohin</t>
+          <t>Omine Akira</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>岡本松浜</t>
+          <t>大峯あきら</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -8110,17 +8105,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>omine-akira</t>
+          <t>omori-domei</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Omine Akira</t>
+          <t>Omori Domei</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>大峯あきら</t>
+          <t>大森桐明</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -8132,17 +8127,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>omori-domei</t>
+          <t>otokuni</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Omori Domei</t>
+          <t>Otokuni</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>大森桐明</t>
+          <t>乙由</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -8154,17 +8149,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>otokuni</t>
+          <t>saio</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Otokuni</t>
+          <t>Saiō</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>乙由</t>
+          <t>西翁</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -8176,17 +8171,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>saio</t>
+          <t>sakaba-aijin</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Saiō</t>
+          <t>Sakaba Aijin</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>西翁</t>
+          <t>酒葉露人</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -8198,17 +8193,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>sakaba-aijin</t>
+          <t>sano-ryota</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Sakaba Aijin</t>
+          <t>Sano Ryota</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>酒葉露人</t>
+          <t>佐野良太</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -8220,17 +8215,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>sano-ryota</t>
+          <t>sawaki-kinichi</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Sano Ryota</t>
+          <t>Sawaki Kinichi</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>佐野良太</t>
+          <t>澤木欣一</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -8242,17 +8237,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>sawaki-kinichi</t>
+          <t>seifu</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Sawaki Kinichi</t>
+          <t>Seifu</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>澤木欣一</t>
+          <t>星布</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -8264,17 +8259,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>seifu</t>
+          <t>shara</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Seifu</t>
+          <t>Shara</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>星布</t>
+          <t>舎羅</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -8286,17 +8281,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>shara</t>
+          <t>shimada-seiho</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Shara</t>
+          <t>Shimada Seiho</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>舎羅</t>
+          <t>島田青峰</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -8308,17 +8303,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>shimada-seiho</t>
+          <t>shoi</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Shimada Seiho</t>
+          <t>Shōi</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>島田青峰</t>
+          <t>松意</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -8330,17 +8325,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>shoi</t>
+          <t>shosatsu</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Shōi</t>
+          <t>Shōsatsu</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>松意</t>
+          <t>正察</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -8352,17 +8347,17 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>shosatsu</t>
+          <t>taimu</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Shōsatsu</t>
+          <t>Taimu</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>正察</t>
+          <t>太無</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -8374,17 +8369,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>taimu</t>
+          <t>takada-choi</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Taimu</t>
+          <t>Takada Choi</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>太無</t>
+          <t>高田蝶衣</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -8396,17 +8391,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>takada-choi</t>
+          <t>takahashi-awajijo</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Takada Choi</t>
+          <t>Takahashi Awajijo</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>高田蝶衣</t>
+          <t>高橋淡路女</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -8418,17 +8413,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>takahashi-awajijo</t>
+          <t>tanaka-ojo</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Takahashi Awajijo</t>
+          <t>Tanaka Ojo</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>高橋淡路女</t>
+          <t>田中王城</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -8440,17 +8435,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>tanaka-ojo</t>
+          <t>tayo</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Tanaka Ojo</t>
+          <t>Tayo</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>田中王城</t>
+          <t>多代女</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -8462,17 +8457,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>tayo</t>
+          <t>tsuruyuki</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Tayo</t>
+          <t>Tsuruyuki</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>多代女</t>
+          <t>鶴永</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -8484,17 +8479,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>tsuruyuki</t>
+          <t>uchida-bojo</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Tsuruyuki</t>
+          <t>Uchida Bojo</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>鶴永</t>
+          <t>内田暮情</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -8506,17 +8501,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>uchida-bojo</t>
+          <t>ueno-yasushi</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Uchida Bojo</t>
+          <t>Ueno Yasushi</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>内田暮情</t>
+          <t>上野泰</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -8528,17 +8523,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ueno-yasushi</t>
+          <t>yoshioka-zenjido</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Ueno Yasushi</t>
+          <t>Yoshioka Zenjido</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>上野泰</t>
+          <t>吉岡禅寺洞</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -8550,42 +8545,20 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>yoshioka-zenjido</t>
+          <t>yuriyama-uko</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Yoshioka Zenjido</t>
+          <t>Yuriyama Uko</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>吉岡禅寺洞</t>
+          <t>百合山羽公</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
-        <is>
-          <t>Modern</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>yuriyama-uko</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Yuriyama Uko</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>百合山羽公</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
         <is>
           <t>Modern</t>
         </is>
@@ -8602,7 +8575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8860,7 +8833,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kato-kyodai</t>
+          <t>kumura-gyotai</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -9080,7 +9053,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kato-kyodai</t>
+          <t>kumura-gyotai</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -10472,6 +10445,28 @@
       <c r="D85" t="inlineStr">
         <is>
           <t>kanji</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>kato-kyodai</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Katō Kyōdai</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>kumura-gyotai</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>manual</t>
         </is>
       </c>
     </row>

--- a/poets_canonical.xlsx
+++ b/poets_canonical.xlsx
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kyōtai</t>
+          <t>Kumura Kyōtai</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">

--- a/poets_canonical.xlsx
+++ b/poets_canonical.xlsx
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>暁台</t>
+          <t>久村暁台</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
